--- a/Excel_Source.xlsx
+++ b/Excel_Source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Heba\Desktop\Payslip final\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Payroll Slip App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C252483C-24A2-49D8-9F9E-F09513B86663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB793F0-6067-40B1-B33C-0918A30704ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Standard Sheet'!$A$1:$AG$51</definedName>
     <definedName name="EmployeeList">_xlfn.ANCHORARRAY([1]List!$F$1)</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -651,7 +652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -689,7 +690,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1566,7 +1566,7 @@
     <col min="33" max="33" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>31</v>
       </c>
@@ -1669,2224 +1669,2224 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
-        <v>100001</v>
+        <v>100009</v>
       </c>
       <c r="B2" s="4">
-        <v>100001</v>
+        <v>100011</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="D2" s="4">
-        <v>7009</v>
+        <v>211</v>
       </c>
       <c r="E2" s="4">
-        <v>7005</v>
+        <v>3256</v>
       </c>
       <c r="F2" s="4">
-        <v>7409</v>
+        <v>10092</v>
       </c>
       <c r="G2" s="4">
-        <v>13866</v>
+        <v>3098</v>
       </c>
       <c r="H2" s="4">
-        <v>4542</v>
+        <v>12211</v>
       </c>
       <c r="I2" s="4">
-        <v>2271</v>
+        <v>4246</v>
       </c>
       <c r="J2" s="4">
-        <v>2402</v>
+        <v>737</v>
       </c>
       <c r="K2" s="4">
-        <v>1162</v>
+        <v>2458</v>
       </c>
       <c r="L2" s="4">
-        <v>12524</v>
+        <v>701</v>
       </c>
       <c r="M2" s="4">
-        <v>100001</v>
+        <v>100011</v>
       </c>
       <c r="N2" s="4">
-        <v>1047</v>
+        <v>2102</v>
       </c>
       <c r="O2" s="4">
-        <v>3087</v>
+        <v>2610</v>
       </c>
       <c r="P2" s="4">
-        <v>2223</v>
+        <v>12035</v>
       </c>
       <c r="Q2" s="4">
-        <v>10651</v>
+        <v>8725</v>
       </c>
       <c r="R2" s="4">
-        <v>4746</v>
+        <v>4856</v>
       </c>
       <c r="S2" s="4">
-        <v>6232</v>
+        <v>11326</v>
       </c>
       <c r="T2" s="4">
-        <v>774</v>
+        <v>1004</v>
       </c>
       <c r="U2" s="4">
-        <v>10762</v>
+        <v>2155</v>
       </c>
       <c r="V2" s="4">
-        <v>6218</v>
+        <v>7815</v>
       </c>
       <c r="W2" s="4">
-        <v>14299</v>
+        <v>5459</v>
       </c>
       <c r="X2" s="4">
-        <v>12265</v>
+        <v>5857</v>
       </c>
       <c r="Y2" s="4">
-        <v>7833</v>
+        <v>883</v>
       </c>
       <c r="Z2" s="4">
-        <v>6390</v>
+        <v>1272</v>
       </c>
       <c r="AA2" s="4">
-        <v>7597</v>
+        <v>11827</v>
       </c>
       <c r="AB2" s="4">
-        <v>10488</v>
+        <v>5568</v>
       </c>
       <c r="AC2" s="4">
-        <v>8492</v>
+        <v>7791</v>
       </c>
       <c r="AD2" s="4">
-        <v>12067</v>
+        <v>8741</v>
       </c>
       <c r="AE2" s="4">
-        <v>5030</v>
+        <v>6583</v>
       </c>
       <c r="AF2" s="4">
-        <v>5063</v>
+        <v>4255</v>
       </c>
       <c r="AG2" s="4">
-        <v>11405</v>
+        <v>8359</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <v>100002</v>
+        <v>100022</v>
       </c>
       <c r="B3" s="4">
-        <v>100002</v>
+        <v>100022</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="D3" s="4">
-        <v>11398</v>
+        <v>211</v>
       </c>
       <c r="E3" s="4">
-        <v>927</v>
+        <v>3427</v>
       </c>
       <c r="F3" s="4">
-        <v>8118</v>
+        <v>8301</v>
       </c>
       <c r="G3" s="4">
-        <v>5822</v>
+        <v>5203</v>
       </c>
       <c r="H3" s="4">
-        <v>14680</v>
+        <v>8225</v>
       </c>
       <c r="I3" s="4">
-        <v>12429</v>
+        <v>5726</v>
       </c>
       <c r="J3" s="4">
-        <v>10233</v>
+        <v>13191</v>
       </c>
       <c r="K3" s="4">
-        <v>14264</v>
+        <v>10102</v>
       </c>
       <c r="L3" s="4">
-        <v>1602</v>
+        <v>2057</v>
       </c>
       <c r="M3" s="4">
-        <v>100002</v>
+        <v>100022</v>
       </c>
       <c r="N3" s="4">
+        <v>2206</v>
+      </c>
+      <c r="O3" s="4">
+        <v>4083</v>
+      </c>
+      <c r="P3" s="4">
+        <v>12180</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>5849</v>
+      </c>
+      <c r="R3" s="4">
+        <v>3749</v>
+      </c>
+      <c r="S3" s="4">
+        <v>838</v>
+      </c>
+      <c r="T3" s="4">
         <v>0</v>
       </c>
-      <c r="O3" s="4">
-        <v>6372</v>
-      </c>
-      <c r="P3" s="4">
-        <v>1229</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>6753</v>
-      </c>
-      <c r="R3" s="4">
-        <v>12658</v>
-      </c>
-      <c r="S3" s="4">
-        <v>6362</v>
-      </c>
-      <c r="T3" s="4">
-        <v>2066</v>
-      </c>
       <c r="U3" s="4">
-        <v>1286</v>
+        <v>8841</v>
       </c>
       <c r="V3" s="4">
-        <v>3231</v>
+        <v>6702</v>
       </c>
       <c r="W3" s="4">
-        <v>82</v>
+        <v>9791</v>
       </c>
       <c r="X3" s="4">
-        <v>4382</v>
+        <v>3592</v>
       </c>
       <c r="Y3" s="4">
-        <v>10439</v>
+        <v>11271</v>
       </c>
       <c r="Z3" s="4">
-        <v>5200</v>
+        <v>8729</v>
       </c>
       <c r="AA3" s="4">
-        <v>1230</v>
+        <v>8802</v>
       </c>
       <c r="AB3" s="4">
-        <v>12004</v>
+        <v>4423</v>
       </c>
       <c r="AC3" s="4">
-        <v>11826</v>
+        <v>14070</v>
       </c>
       <c r="AD3" s="4">
-        <v>4405</v>
+        <v>2885</v>
       </c>
       <c r="AE3" s="4">
-        <v>10788</v>
+        <v>874</v>
       </c>
       <c r="AF3" s="4">
-        <v>13555</v>
+        <v>7996</v>
       </c>
       <c r="AG3" s="4">
-        <v>327</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
-        <v>100003</v>
+        <v>100034</v>
       </c>
       <c r="B4" s="4">
-        <v>100003</v>
+        <v>100034</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="D4" s="4">
-        <v>13588</v>
+        <v>211</v>
       </c>
       <c r="E4" s="4">
-        <v>3311</v>
+        <v>4409</v>
       </c>
       <c r="F4" s="4">
-        <v>9698</v>
+        <v>10894</v>
       </c>
       <c r="G4" s="4">
-        <v>13581</v>
+        <v>10830</v>
       </c>
       <c r="H4" s="4">
-        <v>433</v>
+        <v>10146</v>
       </c>
       <c r="I4" s="4">
-        <v>755</v>
+        <v>12711</v>
       </c>
       <c r="J4" s="4">
-        <v>3741</v>
+        <v>2445</v>
       </c>
       <c r="K4" s="4">
-        <v>13685</v>
+        <v>3611</v>
       </c>
       <c r="L4" s="4">
-        <v>10181</v>
+        <v>5354</v>
       </c>
       <c r="M4" s="4">
-        <v>100003</v>
+        <v>100034</v>
       </c>
       <c r="N4" s="4">
-        <v>0</v>
+        <v>572</v>
       </c>
       <c r="O4" s="4">
-        <v>4117</v>
+        <v>5720</v>
       </c>
       <c r="P4" s="4">
-        <v>13539</v>
+        <v>3219</v>
       </c>
       <c r="Q4" s="4">
-        <v>13901</v>
+        <v>14167</v>
       </c>
       <c r="R4" s="4">
-        <v>2050</v>
+        <v>8444</v>
       </c>
       <c r="S4" s="4">
-        <v>2061</v>
+        <v>8585</v>
       </c>
       <c r="T4" s="4">
-        <v>1371</v>
+        <v>503</v>
       </c>
       <c r="U4" s="4">
-        <v>12539</v>
+        <v>14427</v>
       </c>
       <c r="V4" s="4">
-        <v>9134</v>
+        <v>3252</v>
       </c>
       <c r="W4" s="4">
-        <v>9294</v>
+        <v>5425</v>
       </c>
       <c r="X4" s="4">
-        <v>455</v>
+        <v>4896</v>
       </c>
       <c r="Y4" s="4">
-        <v>3945</v>
+        <v>2977</v>
       </c>
       <c r="Z4" s="4">
-        <v>8402</v>
+        <v>3219</v>
       </c>
       <c r="AA4" s="4">
-        <v>14724</v>
+        <v>7824</v>
       </c>
       <c r="AB4" s="4">
-        <v>11481</v>
+        <v>13226</v>
       </c>
       <c r="AC4" s="4">
-        <v>4181</v>
+        <v>5562</v>
       </c>
       <c r="AD4" s="4">
-        <v>4229</v>
+        <v>8195</v>
       </c>
       <c r="AE4" s="4">
-        <v>2092</v>
+        <v>5419</v>
       </c>
       <c r="AF4" s="4">
-        <v>8372</v>
+        <v>10811</v>
       </c>
       <c r="AG4" s="4">
-        <v>80</v>
+        <v>10875</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>100004</v>
+        <v>100043</v>
       </c>
       <c r="B5" s="4">
-        <v>100004</v>
+        <v>100043</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="D5" s="4">
-        <v>7373</v>
+        <v>211</v>
       </c>
       <c r="E5" s="4">
-        <v>10390</v>
+        <v>4309</v>
       </c>
       <c r="F5" s="4">
-        <v>2576</v>
+        <v>5415</v>
       </c>
       <c r="G5" s="4">
-        <v>7111</v>
+        <v>8939</v>
       </c>
       <c r="H5" s="4">
-        <v>14539</v>
+        <v>10404</v>
       </c>
       <c r="I5" s="4">
-        <v>5438</v>
+        <v>11350</v>
       </c>
       <c r="J5" s="4">
-        <v>13982</v>
+        <v>14400</v>
       </c>
       <c r="K5" s="4">
-        <v>11222</v>
+        <v>14232</v>
       </c>
       <c r="L5" s="4">
-        <v>13463</v>
+        <v>6263</v>
       </c>
       <c r="M5" s="4">
-        <v>100004</v>
+        <v>100043</v>
       </c>
       <c r="N5" s="4">
+        <v>2488</v>
+      </c>
+      <c r="O5" s="4">
+        <v>7771</v>
+      </c>
+      <c r="P5" s="4">
+        <v>13783</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>724</v>
+      </c>
+      <c r="R5" s="4">
+        <v>13128</v>
+      </c>
+      <c r="S5" s="4">
+        <v>3053</v>
+      </c>
+      <c r="T5" s="4">
         <v>0</v>
       </c>
-      <c r="O5" s="4">
-        <v>12886</v>
-      </c>
-      <c r="P5" s="4">
-        <v>957</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>13603</v>
-      </c>
-      <c r="R5" s="4">
-        <v>13677</v>
-      </c>
-      <c r="S5" s="4">
-        <v>10328</v>
-      </c>
-      <c r="T5" s="4">
-        <v>1020</v>
-      </c>
       <c r="U5" s="4">
-        <v>4911</v>
+        <v>6159</v>
       </c>
       <c r="V5" s="4">
-        <v>3148</v>
+        <v>10574</v>
       </c>
       <c r="W5" s="4">
-        <v>4666</v>
+        <v>1557</v>
       </c>
       <c r="X5" s="4">
-        <v>1848</v>
+        <v>9476</v>
       </c>
       <c r="Y5" s="4">
-        <v>6053</v>
+        <v>4902</v>
       </c>
       <c r="Z5" s="4">
-        <v>11509</v>
+        <v>5177</v>
       </c>
       <c r="AA5" s="4">
-        <v>10482</v>
+        <v>7145</v>
       </c>
       <c r="AB5" s="4">
-        <v>12388</v>
+        <v>7200</v>
       </c>
       <c r="AC5" s="4">
-        <v>8930</v>
+        <v>9575</v>
       </c>
       <c r="AD5" s="4">
-        <v>255</v>
+        <v>5784</v>
       </c>
       <c r="AE5" s="4">
-        <v>10857</v>
+        <v>12903</v>
       </c>
       <c r="AF5" s="4">
-        <v>13375</v>
+        <v>157</v>
       </c>
       <c r="AG5" s="4">
-        <v>9654</v>
+        <v>9207</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <v>100005</v>
+        <v>100031</v>
       </c>
       <c r="B6" s="4">
-        <v>100005</v>
+        <v>100031</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="D6" s="4">
-        <v>11445</v>
+        <v>211</v>
       </c>
       <c r="E6" s="4">
-        <v>1103</v>
+        <v>9864</v>
       </c>
       <c r="F6" s="4">
-        <v>4522</v>
+        <v>12614</v>
       </c>
       <c r="G6" s="4">
-        <v>10791</v>
+        <v>241</v>
       </c>
       <c r="H6" s="4">
-        <v>12233</v>
+        <v>14626</v>
       </c>
       <c r="I6" s="4">
-        <v>3495</v>
+        <v>427</v>
       </c>
       <c r="J6" s="4">
-        <v>11423</v>
+        <v>9967</v>
       </c>
       <c r="K6" s="4">
-        <v>3604</v>
+        <v>12454</v>
       </c>
       <c r="L6" s="4">
-        <v>14908</v>
+        <v>10408</v>
       </c>
       <c r="M6" s="4">
-        <v>100005</v>
+        <v>100031</v>
       </c>
       <c r="N6" s="4">
-        <v>1006</v>
+        <v>1121</v>
       </c>
       <c r="O6" s="4">
-        <v>10369</v>
+        <v>8170</v>
       </c>
       <c r="P6" s="4">
-        <v>11579</v>
+        <v>5070</v>
       </c>
       <c r="Q6" s="4">
-        <v>13239</v>
+        <v>10421</v>
       </c>
       <c r="R6" s="4">
-        <v>10010</v>
+        <v>409</v>
       </c>
       <c r="S6" s="4">
-        <v>14924</v>
+        <v>10573</v>
       </c>
       <c r="T6" s="4">
-        <v>1307</v>
+        <v>222</v>
       </c>
       <c r="U6" s="4">
-        <v>14667</v>
+        <v>7635</v>
       </c>
       <c r="V6" s="4">
-        <v>5464</v>
+        <v>6322</v>
       </c>
       <c r="W6" s="4">
-        <v>1238</v>
+        <v>14300</v>
       </c>
       <c r="X6" s="4">
-        <v>3765</v>
+        <v>3022</v>
       </c>
       <c r="Y6" s="4">
-        <v>872</v>
+        <v>14013</v>
       </c>
       <c r="Z6" s="4">
-        <v>11045</v>
+        <v>515</v>
       </c>
       <c r="AA6" s="4">
-        <v>789</v>
+        <v>5033</v>
       </c>
       <c r="AB6" s="4">
-        <v>7228</v>
+        <v>2292</v>
       </c>
       <c r="AC6" s="4">
-        <v>9577</v>
+        <v>7824</v>
       </c>
       <c r="AD6" s="4">
-        <v>11776</v>
+        <v>13252</v>
       </c>
       <c r="AE6" s="4">
-        <v>5756</v>
+        <v>7365</v>
       </c>
       <c r="AF6" s="4">
-        <v>9044</v>
+        <v>11596</v>
       </c>
       <c r="AG6" s="4">
-        <v>303</v>
+        <v>7422</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <v>100006</v>
+        <v>100021</v>
       </c>
       <c r="B7" s="4">
-        <v>100006</v>
+        <v>100021</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="D7" s="4">
-        <v>13384</v>
+        <v>211</v>
       </c>
       <c r="E7" s="4">
-        <v>1228</v>
+        <v>11101</v>
       </c>
       <c r="F7" s="4">
-        <v>1885</v>
+        <v>1136</v>
       </c>
       <c r="G7" s="4">
-        <v>5655</v>
+        <v>3397</v>
       </c>
       <c r="H7" s="4">
-        <v>13891</v>
+        <v>11309</v>
       </c>
       <c r="I7" s="4">
-        <v>3756</v>
+        <v>9316</v>
       </c>
       <c r="J7" s="4">
-        <v>5810</v>
+        <v>10344</v>
       </c>
       <c r="K7" s="4">
-        <v>8463</v>
+        <v>8100</v>
       </c>
       <c r="L7" s="4">
-        <v>8447</v>
+        <v>8172</v>
       </c>
       <c r="M7" s="4">
-        <v>100006</v>
+        <v>100021</v>
       </c>
       <c r="N7" s="4">
-        <v>0</v>
+        <v>363</v>
       </c>
       <c r="O7" s="4">
-        <v>11907</v>
+        <v>14168</v>
       </c>
       <c r="P7" s="4">
-        <v>14200</v>
+        <v>2985</v>
       </c>
       <c r="Q7" s="4">
-        <v>3350</v>
+        <v>10875</v>
       </c>
       <c r="R7" s="4">
-        <v>9666</v>
+        <v>3066</v>
       </c>
       <c r="S7" s="4">
-        <v>1730</v>
+        <v>11857</v>
       </c>
       <c r="T7" s="4">
-        <v>1764</v>
+        <v>1418</v>
       </c>
       <c r="U7" s="4">
-        <v>2357</v>
+        <v>6395</v>
       </c>
       <c r="V7" s="4">
-        <v>10889</v>
+        <v>3316</v>
       </c>
       <c r="W7" s="4">
-        <v>5571</v>
+        <v>4530</v>
       </c>
       <c r="X7" s="4">
-        <v>8249</v>
+        <v>7723</v>
       </c>
       <c r="Y7" s="4">
-        <v>5282</v>
+        <v>7100</v>
       </c>
       <c r="Z7" s="4">
-        <v>13987</v>
+        <v>14983</v>
       </c>
       <c r="AA7" s="4">
-        <v>3339</v>
+        <v>4519</v>
       </c>
       <c r="AB7" s="4">
-        <v>13347</v>
+        <v>582</v>
       </c>
       <c r="AC7" s="4">
-        <v>11421</v>
+        <v>7752</v>
       </c>
       <c r="AD7" s="4">
-        <v>10176</v>
+        <v>13958</v>
       </c>
       <c r="AE7" s="4">
-        <v>5965</v>
+        <v>9016</v>
       </c>
       <c r="AF7" s="4">
-        <v>2178</v>
+        <v>12055</v>
       </c>
       <c r="AG7" s="4">
-        <v>6857</v>
+        <v>9312</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <v>100007</v>
+        <v>100009</v>
       </c>
       <c r="B8" s="4">
-        <v>100007</v>
+        <v>100009</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D8" s="4">
-        <v>5819</v>
+        <v>211</v>
       </c>
       <c r="E8" s="4">
-        <v>12570</v>
+        <v>2773</v>
       </c>
       <c r="F8" s="4">
-        <v>11529</v>
+        <v>2101</v>
       </c>
       <c r="G8" s="4">
-        <v>5857</v>
+        <v>1331</v>
       </c>
       <c r="H8" s="4">
-        <v>11517</v>
+        <v>1365</v>
       </c>
       <c r="I8" s="4">
-        <v>1693</v>
+        <v>12455</v>
       </c>
       <c r="J8" s="4">
-        <v>2682</v>
+        <v>12017</v>
       </c>
       <c r="K8" s="4">
-        <v>13045</v>
+        <v>12281</v>
       </c>
       <c r="L8" s="4">
-        <v>11281</v>
+        <v>10253</v>
       </c>
       <c r="M8" s="4">
-        <v>100007</v>
+        <v>100009</v>
       </c>
       <c r="N8" s="4">
+        <v>356</v>
+      </c>
+      <c r="O8" s="4">
+        <v>12665</v>
+      </c>
+      <c r="P8" s="4">
+        <v>2954</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>7164</v>
+      </c>
+      <c r="R8" s="4">
+        <v>14926</v>
+      </c>
+      <c r="S8" s="4">
+        <v>9057</v>
+      </c>
+      <c r="T8" s="4">
         <v>0</v>
       </c>
-      <c r="O8" s="4">
-        <v>475</v>
-      </c>
-      <c r="P8" s="4">
-        <v>12152</v>
-      </c>
-      <c r="Q8" s="4">
-        <v>14320</v>
-      </c>
-      <c r="R8" s="4">
-        <v>1365</v>
-      </c>
-      <c r="S8" s="4">
-        <v>7663</v>
-      </c>
-      <c r="T8" s="4">
-        <v>586</v>
-      </c>
       <c r="U8" s="4">
-        <v>8190</v>
+        <v>5449</v>
       </c>
       <c r="V8" s="4">
-        <v>9204</v>
+        <v>6383</v>
       </c>
       <c r="W8" s="4">
-        <v>4413</v>
+        <v>3809</v>
       </c>
       <c r="X8" s="4">
-        <v>150</v>
+        <v>7054</v>
       </c>
       <c r="Y8" s="4">
-        <v>7548</v>
+        <v>3327</v>
       </c>
       <c r="Z8" s="4">
-        <v>12086</v>
+        <v>6836</v>
       </c>
       <c r="AA8" s="4">
-        <v>4155</v>
+        <v>11526</v>
       </c>
       <c r="AB8" s="4">
-        <v>10961</v>
+        <v>12182</v>
       </c>
       <c r="AC8" s="4">
-        <v>8006</v>
+        <v>215</v>
       </c>
       <c r="AD8" s="4">
-        <v>1550</v>
+        <v>4372</v>
       </c>
       <c r="AE8" s="4">
-        <v>8727</v>
+        <v>11256</v>
       </c>
       <c r="AF8" s="4">
-        <v>5790</v>
+        <v>8576</v>
       </c>
       <c r="AG8" s="4">
-        <v>13463</v>
+        <v>5697</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <v>100008</v>
+        <v>100027</v>
       </c>
       <c r="B9" s="4">
-        <v>100008</v>
+        <v>100027</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="D9" s="4">
-        <v>8879</v>
+        <v>211</v>
       </c>
       <c r="E9" s="4">
-        <v>5665</v>
+        <v>5002</v>
       </c>
       <c r="F9" s="4">
-        <v>1413</v>
+        <v>12062</v>
       </c>
       <c r="G9" s="4">
-        <v>14308</v>
+        <v>14451</v>
       </c>
       <c r="H9" s="4">
-        <v>9197</v>
+        <v>11582</v>
       </c>
       <c r="I9" s="4">
-        <v>12968</v>
+        <v>4303</v>
       </c>
       <c r="J9" s="4">
-        <v>11079</v>
+        <v>3177</v>
       </c>
       <c r="K9" s="4">
-        <v>3878</v>
+        <v>13993</v>
       </c>
       <c r="L9" s="4">
-        <v>9527</v>
+        <v>5552</v>
       </c>
       <c r="M9" s="4">
-        <v>100008</v>
+        <v>100027</v>
       </c>
       <c r="N9" s="4">
-        <v>1638</v>
+        <v>380</v>
       </c>
       <c r="O9" s="4">
-        <v>9580</v>
+        <v>6028</v>
       </c>
       <c r="P9" s="4">
-        <v>4286</v>
+        <v>14493</v>
       </c>
       <c r="Q9" s="4">
-        <v>14628</v>
+        <v>1392</v>
       </c>
       <c r="R9" s="4">
-        <v>12712</v>
+        <v>2314</v>
       </c>
       <c r="S9" s="4">
-        <v>6422</v>
+        <v>9267</v>
       </c>
       <c r="T9" s="4">
-        <v>2323</v>
+        <v>0</v>
       </c>
       <c r="U9" s="4">
-        <v>9492</v>
+        <v>2950</v>
       </c>
       <c r="V9" s="4">
-        <v>7664</v>
+        <v>4642</v>
       </c>
       <c r="W9" s="4">
-        <v>2934</v>
+        <v>973</v>
       </c>
       <c r="X9" s="4">
-        <v>5692</v>
+        <v>5032</v>
       </c>
       <c r="Y9" s="4">
-        <v>14526</v>
+        <v>874</v>
       </c>
       <c r="Z9" s="4">
-        <v>4612</v>
+        <v>3732</v>
       </c>
       <c r="AA9" s="4">
-        <v>2757</v>
+        <v>7188</v>
       </c>
       <c r="AB9" s="4">
-        <v>5989</v>
+        <v>2099</v>
       </c>
       <c r="AC9" s="4">
-        <v>8718</v>
+        <v>6125</v>
       </c>
       <c r="AD9" s="4">
-        <v>10611</v>
+        <v>6403</v>
       </c>
       <c r="AE9" s="4">
-        <v>7261</v>
+        <v>1441</v>
       </c>
       <c r="AF9" s="4">
-        <v>1931</v>
+        <v>10064</v>
       </c>
       <c r="AG9" s="4">
-        <v>12570</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <v>100009</v>
+        <v>100033</v>
       </c>
       <c r="B10" s="4">
-        <v>100009</v>
+        <v>100033</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="D10" s="4">
-        <v>2312</v>
+        <v>211</v>
       </c>
       <c r="E10" s="4">
-        <v>2773</v>
+        <v>2087</v>
       </c>
       <c r="F10" s="4">
-        <v>2101</v>
+        <v>2682</v>
       </c>
       <c r="G10" s="4">
-        <v>1331</v>
+        <v>2332</v>
       </c>
       <c r="H10" s="4">
-        <v>1365</v>
+        <v>4096</v>
       </c>
       <c r="I10" s="4">
-        <v>12455</v>
+        <v>14322</v>
       </c>
       <c r="J10" s="4">
-        <v>12017</v>
+        <v>10485</v>
       </c>
       <c r="K10" s="4">
-        <v>12281</v>
+        <v>14146</v>
       </c>
       <c r="L10" s="4">
-        <v>10253</v>
+        <v>7369</v>
       </c>
       <c r="M10" s="4">
-        <v>100009</v>
+        <v>100033</v>
       </c>
       <c r="N10" s="4">
-        <v>356</v>
+        <v>1804</v>
       </c>
       <c r="O10" s="4">
-        <v>12665</v>
+        <v>8153</v>
       </c>
       <c r="P10" s="4">
-        <v>2954</v>
+        <v>6283</v>
       </c>
       <c r="Q10" s="4">
-        <v>7164</v>
+        <v>3246</v>
       </c>
       <c r="R10" s="4">
-        <v>14926</v>
+        <v>12036</v>
       </c>
       <c r="S10" s="4">
-        <v>9057</v>
+        <v>12812</v>
       </c>
       <c r="T10" s="4">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="U10" s="4">
-        <v>5449</v>
+        <v>9151</v>
       </c>
       <c r="V10" s="4">
-        <v>6383</v>
+        <v>13443</v>
       </c>
       <c r="W10" s="4">
-        <v>3809</v>
+        <v>66</v>
       </c>
       <c r="X10" s="4">
-        <v>7054</v>
+        <v>14894</v>
       </c>
       <c r="Y10" s="4">
-        <v>3327</v>
+        <v>14554</v>
       </c>
       <c r="Z10" s="4">
-        <v>6836</v>
+        <v>8268</v>
       </c>
       <c r="AA10" s="4">
-        <v>11526</v>
+        <v>8833</v>
       </c>
       <c r="AB10" s="4">
-        <v>12182</v>
+        <v>11153</v>
       </c>
       <c r="AC10" s="4">
-        <v>215</v>
+        <v>2047</v>
       </c>
       <c r="AD10" s="4">
-        <v>4372</v>
+        <v>311</v>
       </c>
       <c r="AE10" s="4">
-        <v>11256</v>
+        <v>9319</v>
       </c>
       <c r="AF10" s="4">
-        <v>8576</v>
+        <v>11424</v>
       </c>
       <c r="AG10" s="4">
-        <v>5697</v>
+        <v>12653</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <v>100010</v>
+        <v>100048</v>
       </c>
       <c r="B11" s="4">
-        <v>100010</v>
+        <v>100048</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="D11" s="4">
-        <v>9223</v>
+        <v>211</v>
       </c>
       <c r="E11" s="4">
-        <v>9733</v>
+        <v>769</v>
       </c>
       <c r="F11" s="4">
-        <v>1553</v>
+        <v>3951</v>
       </c>
       <c r="G11" s="4">
-        <v>9891</v>
+        <v>5730</v>
       </c>
       <c r="H11" s="4">
-        <v>13978</v>
+        <v>7578</v>
       </c>
       <c r="I11" s="4">
-        <v>2736</v>
+        <v>13615</v>
       </c>
       <c r="J11" s="4">
-        <v>901</v>
+        <v>8746</v>
       </c>
       <c r="K11" s="4">
-        <v>4237</v>
+        <v>9040</v>
       </c>
       <c r="L11" s="4">
-        <v>11291</v>
+        <v>12315</v>
       </c>
       <c r="M11" s="4">
-        <v>100010</v>
+        <v>100048</v>
       </c>
       <c r="N11" s="4">
-        <v>1943</v>
+        <v>2954</v>
       </c>
       <c r="O11" s="4">
-        <v>8545</v>
+        <v>7201</v>
       </c>
       <c r="P11" s="4">
-        <v>5809</v>
+        <v>12085</v>
       </c>
       <c r="Q11" s="4">
-        <v>9538</v>
+        <v>6377</v>
       </c>
       <c r="R11" s="4">
-        <v>6887</v>
+        <v>9557</v>
       </c>
       <c r="S11" s="4">
-        <v>13211</v>
+        <v>13154</v>
       </c>
       <c r="T11" s="4">
-        <v>1095</v>
+        <v>0</v>
       </c>
       <c r="U11" s="4">
-        <v>7513</v>
+        <v>7097</v>
       </c>
       <c r="V11" s="4">
-        <v>1903</v>
+        <v>14508</v>
       </c>
       <c r="W11" s="4">
-        <v>8028</v>
+        <v>3142</v>
       </c>
       <c r="X11" s="4">
-        <v>4792</v>
+        <v>7133</v>
       </c>
       <c r="Y11" s="4">
-        <v>2798</v>
+        <v>7742</v>
       </c>
       <c r="Z11" s="4">
-        <v>9759</v>
+        <v>5684</v>
       </c>
       <c r="AA11" s="4">
-        <v>9644</v>
+        <v>4322</v>
       </c>
       <c r="AB11" s="4">
-        <v>793</v>
+        <v>1054</v>
       </c>
       <c r="AC11" s="4">
-        <v>10522</v>
+        <v>9564</v>
       </c>
       <c r="AD11" s="4">
-        <v>6990</v>
+        <v>11893</v>
       </c>
       <c r="AE11" s="4">
-        <v>9297</v>
+        <v>7529</v>
       </c>
       <c r="AF11" s="4">
-        <v>7812</v>
+        <v>5701</v>
       </c>
       <c r="AG11" s="4">
-        <v>5121</v>
+        <v>10859</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
-        <v>100011</v>
+        <v>100030</v>
       </c>
       <c r="B12" s="4">
-        <v>100011</v>
+        <v>100030</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="D12" s="4">
         <v>211</v>
       </c>
       <c r="E12" s="4">
-        <v>3256</v>
+        <v>1851</v>
       </c>
       <c r="F12" s="4">
-        <v>10092</v>
+        <v>696</v>
       </c>
       <c r="G12" s="4">
-        <v>3098</v>
+        <v>2588</v>
       </c>
       <c r="H12" s="4">
-        <v>12211</v>
+        <v>2257</v>
       </c>
       <c r="I12" s="4">
-        <v>4246</v>
+        <v>6448</v>
       </c>
       <c r="J12" s="4">
-        <v>737</v>
+        <v>8034</v>
       </c>
       <c r="K12" s="4">
-        <v>2458</v>
+        <v>4823</v>
       </c>
       <c r="L12" s="4">
-        <v>701</v>
+        <v>1196</v>
       </c>
       <c r="M12" s="4">
-        <v>100011</v>
+        <v>100030</v>
       </c>
       <c r="N12" s="4">
-        <v>2102</v>
+        <v>0</v>
       </c>
       <c r="O12" s="4">
-        <v>2610</v>
+        <v>9864</v>
       </c>
       <c r="P12" s="4">
-        <v>12035</v>
+        <v>8602</v>
       </c>
       <c r="Q12" s="4">
-        <v>8725</v>
+        <v>2313</v>
       </c>
       <c r="R12" s="4">
-        <v>4856</v>
+        <v>13099</v>
       </c>
       <c r="S12" s="4">
-        <v>11326</v>
+        <v>12109</v>
       </c>
       <c r="T12" s="4">
-        <v>1004</v>
+        <v>311</v>
       </c>
       <c r="U12" s="4">
-        <v>2155</v>
+        <v>4885</v>
       </c>
       <c r="V12" s="4">
-        <v>7815</v>
+        <v>3251</v>
       </c>
       <c r="W12" s="4">
-        <v>5459</v>
+        <v>5022</v>
       </c>
       <c r="X12" s="4">
-        <v>5857</v>
+        <v>11661</v>
       </c>
       <c r="Y12" s="4">
-        <v>883</v>
+        <v>4968</v>
       </c>
       <c r="Z12" s="4">
-        <v>1272</v>
+        <v>8583</v>
       </c>
       <c r="AA12" s="4">
-        <v>11827</v>
+        <v>276</v>
       </c>
       <c r="AB12" s="4">
-        <v>5568</v>
+        <v>4813</v>
       </c>
       <c r="AC12" s="4">
-        <v>7791</v>
+        <v>8408</v>
       </c>
       <c r="AD12" s="4">
-        <v>8741</v>
+        <v>11700</v>
       </c>
       <c r="AE12" s="4">
-        <v>6583</v>
+        <v>11193</v>
       </c>
       <c r="AF12" s="4">
-        <v>4255</v>
+        <v>4826</v>
       </c>
       <c r="AG12" s="4">
-        <v>8359</v>
+        <v>10215</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <v>100012</v>
+        <v>100050</v>
       </c>
       <c r="B13" s="4">
-        <v>100012</v>
+        <v>100050</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="D13" s="4">
-        <v>11626</v>
+        <v>211</v>
       </c>
       <c r="E13" s="4">
-        <v>12878</v>
+        <v>4056</v>
       </c>
       <c r="F13" s="4">
-        <v>4677</v>
+        <v>14818</v>
       </c>
       <c r="G13" s="4">
-        <v>13037</v>
+        <v>1143</v>
       </c>
       <c r="H13" s="4">
-        <v>6520</v>
+        <v>6108</v>
       </c>
       <c r="I13" s="4">
-        <v>8098</v>
+        <v>14882</v>
       </c>
       <c r="J13" s="4">
-        <v>9238</v>
+        <v>6866</v>
       </c>
       <c r="K13" s="4">
-        <v>11764</v>
+        <v>3352</v>
       </c>
       <c r="L13" s="4">
-        <v>10264</v>
+        <v>12533</v>
       </c>
       <c r="M13" s="4">
-        <v>100012</v>
+        <v>100050</v>
       </c>
       <c r="N13" s="4">
-        <v>1648</v>
+        <v>0</v>
       </c>
       <c r="O13" s="4">
-        <v>3960</v>
+        <v>747</v>
       </c>
       <c r="P13" s="4">
-        <v>10579</v>
+        <v>6987</v>
       </c>
       <c r="Q13" s="4">
-        <v>11117</v>
+        <v>8427</v>
       </c>
       <c r="R13" s="4">
-        <v>10327</v>
+        <v>9481</v>
       </c>
       <c r="S13" s="4">
-        <v>1017</v>
+        <v>1633</v>
       </c>
       <c r="T13" s="4">
-        <v>1585</v>
+        <v>0</v>
       </c>
       <c r="U13" s="4">
-        <v>5765</v>
+        <v>6454</v>
       </c>
       <c r="V13" s="4">
-        <v>4188</v>
+        <v>5567</v>
       </c>
       <c r="W13" s="4">
-        <v>12825</v>
+        <v>10616</v>
       </c>
       <c r="X13" s="4">
-        <v>5708</v>
+        <v>14446</v>
       </c>
       <c r="Y13" s="4">
-        <v>8889</v>
+        <v>12113</v>
       </c>
       <c r="Z13" s="4">
-        <v>12725</v>
+        <v>1893</v>
       </c>
       <c r="AA13" s="4">
-        <v>10692</v>
+        <v>8700</v>
       </c>
       <c r="AB13" s="4">
-        <v>1431</v>
+        <v>6687</v>
       </c>
       <c r="AC13" s="4">
-        <v>10269</v>
+        <v>14803</v>
       </c>
       <c r="AD13" s="4">
-        <v>6722</v>
+        <v>1632</v>
       </c>
       <c r="AE13" s="4">
-        <v>10202</v>
+        <v>9791</v>
       </c>
       <c r="AF13" s="4">
-        <v>1262</v>
+        <v>2177</v>
       </c>
       <c r="AG13" s="4">
-        <v>6870</v>
+        <v>6997</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <v>100013</v>
+        <v>100046</v>
       </c>
       <c r="B14" s="4">
-        <v>100013</v>
+        <v>100046</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>118</v>
+        <v>151</v>
       </c>
       <c r="D14" s="4">
-        <v>8083</v>
+        <v>5421</v>
       </c>
       <c r="E14" s="4">
-        <v>7056</v>
+        <v>7841</v>
       </c>
       <c r="F14" s="4">
-        <v>2488</v>
+        <v>1073</v>
       </c>
       <c r="G14" s="4">
-        <v>11520</v>
+        <v>12205</v>
       </c>
       <c r="H14" s="4">
-        <v>2005</v>
+        <v>168</v>
       </c>
       <c r="I14" s="4">
-        <v>13584</v>
+        <v>5357</v>
       </c>
       <c r="J14" s="4">
-        <v>7027</v>
+        <v>3325</v>
       </c>
       <c r="K14" s="4">
-        <v>8729</v>
+        <v>4608</v>
       </c>
       <c r="L14" s="4">
-        <v>818</v>
+        <v>6166</v>
       </c>
       <c r="M14" s="4">
-        <v>100013</v>
+        <v>100046</v>
       </c>
       <c r="N14" s="4">
-        <v>1707</v>
+        <v>0</v>
       </c>
       <c r="O14" s="4">
-        <v>1449</v>
+        <v>8502</v>
       </c>
       <c r="P14" s="4">
-        <v>8057</v>
+        <v>7982</v>
       </c>
       <c r="Q14" s="4">
-        <v>2195</v>
+        <v>9083</v>
       </c>
       <c r="R14" s="4">
-        <v>2567</v>
+        <v>13973</v>
       </c>
       <c r="S14" s="4">
-        <v>1741</v>
+        <v>1040</v>
       </c>
       <c r="T14" s="4">
-        <v>0</v>
+        <v>2191</v>
       </c>
       <c r="U14" s="4">
-        <v>9576</v>
+        <v>12976</v>
       </c>
       <c r="V14" s="4">
-        <v>6433</v>
+        <v>2563</v>
       </c>
       <c r="W14" s="4">
-        <v>14299</v>
+        <v>4521</v>
       </c>
       <c r="X14" s="4">
-        <v>7892</v>
+        <v>624</v>
       </c>
       <c r="Y14" s="4">
-        <v>11301</v>
+        <v>12180</v>
       </c>
       <c r="Z14" s="4">
-        <v>9695</v>
+        <v>12757</v>
       </c>
       <c r="AA14" s="4">
-        <v>1391</v>
+        <v>3168</v>
       </c>
       <c r="AB14" s="4">
-        <v>14533</v>
+        <v>14461</v>
       </c>
       <c r="AC14" s="4">
-        <v>8357</v>
+        <v>12657</v>
       </c>
       <c r="AD14" s="4">
-        <v>7357</v>
+        <v>13652</v>
       </c>
       <c r="AE14" s="4">
-        <v>12018</v>
+        <v>13167</v>
       </c>
       <c r="AF14" s="4">
-        <v>12535</v>
+        <v>5624</v>
       </c>
       <c r="AG14" s="4">
-        <v>9544</v>
+        <v>10248</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <v>100014</v>
+        <v>100001</v>
       </c>
       <c r="B15" s="4">
-        <v>100014</v>
+        <v>100007</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D15" s="4">
-        <v>14878</v>
+        <v>5819</v>
       </c>
       <c r="E15" s="4">
-        <v>4362</v>
+        <v>12570</v>
       </c>
       <c r="F15" s="4">
-        <v>9794</v>
+        <v>11529</v>
       </c>
       <c r="G15" s="4">
-        <v>14480</v>
+        <v>5857</v>
       </c>
       <c r="H15" s="4">
-        <v>8152</v>
+        <v>11517</v>
       </c>
       <c r="I15" s="4">
-        <v>792</v>
+        <v>1693</v>
       </c>
       <c r="J15" s="4">
-        <v>8385</v>
+        <v>2682</v>
       </c>
       <c r="K15" s="4">
-        <v>12164</v>
+        <v>13045</v>
       </c>
       <c r="L15" s="4">
-        <v>14688</v>
+        <v>11281</v>
       </c>
       <c r="M15" s="4">
-        <v>100014</v>
+        <v>100007</v>
       </c>
       <c r="N15" s="4">
-        <v>829</v>
+        <v>0</v>
       </c>
       <c r="O15" s="4">
-        <v>6537</v>
+        <v>475</v>
       </c>
       <c r="P15" s="4">
-        <v>119</v>
+        <v>12152</v>
       </c>
       <c r="Q15" s="4">
-        <v>5406</v>
+        <v>14320</v>
       </c>
       <c r="R15" s="4">
-        <v>12292</v>
+        <v>1365</v>
       </c>
       <c r="S15" s="4">
-        <v>11974</v>
+        <v>7663</v>
       </c>
       <c r="T15" s="4">
-        <v>1250</v>
+        <v>586</v>
       </c>
       <c r="U15" s="4">
-        <v>12756</v>
+        <v>8190</v>
       </c>
       <c r="V15" s="4">
-        <v>11320</v>
+        <v>9204</v>
       </c>
       <c r="W15" s="4">
-        <v>2860</v>
+        <v>4413</v>
       </c>
       <c r="X15" s="4">
-        <v>6135</v>
+        <v>150</v>
       </c>
       <c r="Y15" s="4">
-        <v>6951</v>
+        <v>7548</v>
       </c>
       <c r="Z15" s="4">
-        <v>9707</v>
+        <v>12086</v>
       </c>
       <c r="AA15" s="4">
-        <v>14785</v>
+        <v>4155</v>
       </c>
       <c r="AB15" s="4">
-        <v>8055</v>
+        <v>10961</v>
       </c>
       <c r="AC15" s="4">
-        <v>13653</v>
+        <v>8006</v>
       </c>
       <c r="AD15" s="4">
-        <v>5687</v>
+        <v>1550</v>
       </c>
       <c r="AE15" s="4">
-        <v>6968</v>
+        <v>8727</v>
       </c>
       <c r="AF15" s="4">
-        <v>252</v>
+        <v>5790</v>
       </c>
       <c r="AG15" s="4">
-        <v>14194</v>
+        <v>13463</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <v>100015</v>
+        <v>100028</v>
       </c>
       <c r="B16" s="4">
-        <v>100015</v>
+        <v>100028</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="D16" s="4">
-        <v>11902</v>
+        <v>6754</v>
       </c>
       <c r="E16" s="4">
-        <v>13178</v>
+        <v>9902</v>
       </c>
       <c r="F16" s="4">
-        <v>10395</v>
+        <v>2593</v>
       </c>
       <c r="G16" s="4">
-        <v>10529</v>
+        <v>10405</v>
       </c>
       <c r="H16" s="4">
-        <v>298</v>
+        <v>12297</v>
       </c>
       <c r="I16" s="4">
-        <v>12341</v>
+        <v>320</v>
       </c>
       <c r="J16" s="4">
-        <v>9666</v>
+        <v>2205</v>
       </c>
       <c r="K16" s="4">
-        <v>5693</v>
+        <v>12552</v>
       </c>
       <c r="L16" s="4">
-        <v>8412</v>
+        <v>2065</v>
       </c>
       <c r="M16" s="4">
-        <v>100015</v>
+        <v>100028</v>
       </c>
       <c r="N16" s="4">
-        <v>0</v>
+        <v>2241</v>
       </c>
       <c r="O16" s="4">
-        <v>5214</v>
+        <v>7632</v>
       </c>
       <c r="P16" s="4">
-        <v>12755</v>
+        <v>6220</v>
       </c>
       <c r="Q16" s="4">
-        <v>14930</v>
+        <v>10388</v>
       </c>
       <c r="R16" s="4">
-        <v>13548</v>
+        <v>4185</v>
       </c>
       <c r="S16" s="4">
-        <v>1782</v>
+        <v>6907</v>
       </c>
       <c r="T16" s="4">
-        <v>2364</v>
+        <v>1608</v>
       </c>
       <c r="U16" s="4">
-        <v>6173</v>
+        <v>169</v>
       </c>
       <c r="V16" s="4">
-        <v>13094</v>
+        <v>9190</v>
       </c>
       <c r="W16" s="4">
-        <v>2764</v>
+        <v>5120</v>
       </c>
       <c r="X16" s="4">
-        <v>8750</v>
+        <v>6593</v>
       </c>
       <c r="Y16" s="4">
-        <v>647</v>
+        <v>3519</v>
       </c>
       <c r="Z16" s="4">
-        <v>3004</v>
+        <v>2790</v>
       </c>
       <c r="AA16" s="4">
-        <v>2756</v>
+        <v>3417</v>
       </c>
       <c r="AB16" s="4">
-        <v>14278</v>
+        <v>7370</v>
       </c>
       <c r="AC16" s="4">
-        <v>7556</v>
+        <v>12028</v>
       </c>
       <c r="AD16" s="4">
-        <v>4733</v>
+        <v>3728</v>
       </c>
       <c r="AE16" s="4">
-        <v>10396</v>
+        <v>3714</v>
       </c>
       <c r="AF16" s="4">
-        <v>8497</v>
+        <v>3555</v>
       </c>
       <c r="AG16" s="4">
-        <v>8184</v>
+        <v>3275</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <v>100016</v>
+        <v>100026</v>
       </c>
       <c r="B17" s="4">
-        <v>100016</v>
+        <v>100026</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D17" s="4">
-        <v>12254</v>
+        <v>6893</v>
       </c>
       <c r="E17" s="4">
-        <v>2057</v>
+        <v>13593</v>
       </c>
       <c r="F17" s="4">
-        <v>14802</v>
+        <v>1513</v>
       </c>
       <c r="G17" s="4">
-        <v>9822</v>
+        <v>6964</v>
       </c>
       <c r="H17" s="4">
-        <v>5180</v>
+        <v>9619</v>
       </c>
       <c r="I17" s="4">
-        <v>11919</v>
+        <v>9209</v>
       </c>
       <c r="J17" s="4">
-        <v>12656</v>
+        <v>1013</v>
       </c>
       <c r="K17" s="4">
-        <v>3024</v>
+        <v>9209</v>
       </c>
       <c r="L17" s="4">
-        <v>9998</v>
+        <v>6878</v>
       </c>
       <c r="M17" s="4">
-        <v>100016</v>
+        <v>100026</v>
       </c>
       <c r="N17" s="4">
-        <v>2571</v>
+        <v>2095</v>
       </c>
       <c r="O17" s="4">
-        <v>13475</v>
+        <v>12215</v>
       </c>
       <c r="P17" s="4">
-        <v>11319</v>
+        <v>7158</v>
       </c>
       <c r="Q17" s="4">
-        <v>2661</v>
+        <v>1043</v>
       </c>
       <c r="R17" s="4">
-        <v>9746</v>
+        <v>13310</v>
       </c>
       <c r="S17" s="4">
-        <v>11971</v>
+        <v>9280</v>
       </c>
       <c r="T17" s="4">
-        <v>1647</v>
+        <v>0</v>
       </c>
       <c r="U17" s="4">
-        <v>9054</v>
+        <v>2443</v>
       </c>
       <c r="V17" s="4">
-        <v>14340</v>
+        <v>1726</v>
       </c>
       <c r="W17" s="4">
-        <v>12452</v>
+        <v>156</v>
       </c>
       <c r="X17" s="4">
-        <v>340</v>
+        <v>4003</v>
       </c>
       <c r="Y17" s="4">
-        <v>11471</v>
+        <v>9756</v>
       </c>
       <c r="Z17" s="4">
-        <v>2771</v>
+        <v>10504</v>
       </c>
       <c r="AA17" s="4">
-        <v>8911</v>
+        <v>1429</v>
       </c>
       <c r="AB17" s="4">
-        <v>7057</v>
+        <v>10357</v>
       </c>
       <c r="AC17" s="4">
-        <v>12853</v>
+        <v>5782</v>
       </c>
       <c r="AD17" s="4">
-        <v>10684</v>
+        <v>8738</v>
       </c>
       <c r="AE17" s="4">
-        <v>8724</v>
+        <v>8037</v>
       </c>
       <c r="AF17" s="4">
-        <v>3139</v>
+        <v>5544</v>
       </c>
       <c r="AG17" s="4">
-        <v>12150</v>
+        <v>6311</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
-        <v>100017</v>
+        <v>100035</v>
       </c>
       <c r="B18" s="4">
-        <v>100017</v>
+        <v>100035</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="D18" s="4">
-        <v>13336</v>
+        <v>7007</v>
       </c>
       <c r="E18" s="4">
-        <v>7707</v>
+        <v>2233</v>
       </c>
       <c r="F18" s="4">
-        <v>12329</v>
+        <v>14847</v>
       </c>
       <c r="G18" s="4">
-        <v>6981</v>
+        <v>5152</v>
       </c>
       <c r="H18" s="4">
-        <v>920</v>
+        <v>14812</v>
       </c>
       <c r="I18" s="4">
-        <v>10591</v>
+        <v>13869</v>
       </c>
       <c r="J18" s="4">
-        <v>7374</v>
+        <v>13614</v>
       </c>
       <c r="K18" s="4">
-        <v>7704</v>
+        <v>14857</v>
       </c>
       <c r="L18" s="4">
-        <v>4904</v>
+        <v>11253</v>
       </c>
       <c r="M18" s="4">
-        <v>100017</v>
+        <v>100035</v>
       </c>
       <c r="N18" s="4">
-        <v>514</v>
+        <v>1100</v>
       </c>
       <c r="O18" s="4">
-        <v>13364</v>
+        <v>1267</v>
       </c>
       <c r="P18" s="4">
-        <v>14042</v>
+        <v>9192</v>
       </c>
       <c r="Q18" s="4">
-        <v>573</v>
+        <v>7194</v>
       </c>
       <c r="R18" s="4">
-        <v>5785</v>
+        <v>8365</v>
       </c>
       <c r="S18" s="4">
-        <v>3244</v>
+        <v>8479</v>
       </c>
       <c r="T18" s="4">
-        <v>1531</v>
+        <v>830</v>
       </c>
       <c r="U18" s="4">
-        <v>14921</v>
+        <v>1573</v>
       </c>
       <c r="V18" s="4">
-        <v>9354</v>
+        <v>4583</v>
       </c>
       <c r="W18" s="4">
-        <v>5163</v>
+        <v>3192</v>
       </c>
       <c r="X18" s="4">
-        <v>8289</v>
+        <v>2473</v>
       </c>
       <c r="Y18" s="4">
-        <v>11896</v>
+        <v>7351</v>
       </c>
       <c r="Z18" s="4">
-        <v>12191</v>
+        <v>6487</v>
       </c>
       <c r="AA18" s="4">
-        <v>7556</v>
+        <v>7923</v>
       </c>
       <c r="AB18" s="4">
-        <v>9454</v>
+        <v>9951</v>
       </c>
       <c r="AC18" s="4">
-        <v>1721</v>
+        <v>1419</v>
       </c>
       <c r="AD18" s="4">
-        <v>13795</v>
+        <v>6468</v>
       </c>
       <c r="AE18" s="4">
-        <v>14871</v>
+        <v>272</v>
       </c>
       <c r="AF18" s="4">
-        <v>5970</v>
+        <v>13785</v>
       </c>
       <c r="AG18" s="4">
-        <v>14863</v>
+        <v>11345</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
-        <v>100018</v>
+        <v>100001</v>
       </c>
       <c r="B19" s="4">
-        <v>100018</v>
+        <v>100001</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="D19" s="4">
-        <v>13165</v>
+        <v>7009</v>
       </c>
       <c r="E19" s="4">
-        <v>2492</v>
+        <v>7005</v>
       </c>
       <c r="F19" s="4">
-        <v>2719</v>
+        <v>7409</v>
       </c>
       <c r="G19" s="4">
-        <v>2441</v>
+        <v>13866</v>
       </c>
       <c r="H19" s="4">
-        <v>3348</v>
+        <v>4542</v>
       </c>
       <c r="I19" s="4">
-        <v>8110</v>
+        <v>2271</v>
       </c>
       <c r="J19" s="4">
-        <v>13581</v>
+        <v>2402</v>
       </c>
       <c r="K19" s="4">
-        <v>1930</v>
+        <v>1162</v>
       </c>
       <c r="L19" s="4">
-        <v>11697</v>
+        <v>12524</v>
       </c>
       <c r="M19" s="4">
-        <v>100018</v>
+        <v>100001</v>
       </c>
       <c r="N19" s="4">
-        <v>2000</v>
+        <v>1047</v>
       </c>
       <c r="O19" s="4">
-        <v>6205</v>
+        <v>3087</v>
       </c>
       <c r="P19" s="4">
-        <v>14826</v>
+        <v>2223</v>
       </c>
       <c r="Q19" s="4">
-        <v>7925</v>
+        <v>10651</v>
       </c>
       <c r="R19" s="4">
-        <v>1212</v>
+        <v>4746</v>
       </c>
       <c r="S19" s="4">
-        <v>11307</v>
+        <v>6232</v>
       </c>
       <c r="T19" s="4">
-        <v>0</v>
+        <v>774</v>
       </c>
       <c r="U19" s="4">
-        <v>9424</v>
+        <v>10762</v>
       </c>
       <c r="V19" s="4">
-        <v>7037</v>
+        <v>6218</v>
       </c>
       <c r="W19" s="4">
-        <v>11378</v>
+        <v>14299</v>
       </c>
       <c r="X19" s="4">
-        <v>4703</v>
+        <v>12265</v>
       </c>
       <c r="Y19" s="4">
-        <v>14141</v>
+        <v>7833</v>
       </c>
       <c r="Z19" s="4">
-        <v>2415</v>
+        <v>6390</v>
       </c>
       <c r="AA19" s="4">
-        <v>9146</v>
+        <v>7597</v>
       </c>
       <c r="AB19" s="4">
-        <v>14739</v>
+        <v>10488</v>
       </c>
       <c r="AC19" s="4">
-        <v>1716</v>
+        <v>8492</v>
       </c>
       <c r="AD19" s="4">
-        <v>945</v>
+        <v>12067</v>
       </c>
       <c r="AE19" s="4">
-        <v>10244</v>
+        <v>5030</v>
       </c>
       <c r="AF19" s="4">
-        <v>6285</v>
+        <v>5063</v>
       </c>
       <c r="AG19" s="4">
-        <v>2789</v>
+        <v>11405</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
-        <v>100019</v>
+        <v>100040</v>
       </c>
       <c r="B20" s="4">
-        <v>100019</v>
+        <v>100040</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="D20" s="4">
-        <v>12128</v>
+        <v>7094</v>
       </c>
       <c r="E20" s="4">
-        <v>9235</v>
+        <v>373</v>
       </c>
       <c r="F20" s="4">
-        <v>14270</v>
+        <v>660</v>
       </c>
       <c r="G20" s="4">
-        <v>598</v>
+        <v>9045</v>
       </c>
       <c r="H20" s="4">
-        <v>1125</v>
+        <v>10029</v>
       </c>
       <c r="I20" s="4">
-        <v>11412</v>
+        <v>13304</v>
       </c>
       <c r="J20" s="4">
-        <v>13656</v>
+        <v>6575</v>
       </c>
       <c r="K20" s="4">
-        <v>3219</v>
+        <v>7051</v>
       </c>
       <c r="L20" s="4">
-        <v>5261</v>
+        <v>13100</v>
       </c>
       <c r="M20" s="4">
-        <v>100019</v>
+        <v>100040</v>
       </c>
       <c r="N20" s="4">
-        <v>1303</v>
+        <v>1996</v>
       </c>
       <c r="O20" s="4">
-        <v>503</v>
+        <v>3686</v>
       </c>
       <c r="P20" s="4">
-        <v>2646</v>
+        <v>4703</v>
       </c>
       <c r="Q20" s="4">
-        <v>13569</v>
+        <v>5200</v>
       </c>
       <c r="R20" s="4">
-        <v>3367</v>
+        <v>3218</v>
       </c>
       <c r="S20" s="4">
-        <v>4422</v>
+        <v>11205</v>
       </c>
       <c r="T20" s="4">
-        <v>1652</v>
+        <v>746</v>
       </c>
       <c r="U20" s="4">
-        <v>7664</v>
+        <v>14981</v>
       </c>
       <c r="V20" s="4">
-        <v>2715</v>
+        <v>10403</v>
       </c>
       <c r="W20" s="4">
-        <v>5909</v>
+        <v>3287</v>
       </c>
       <c r="X20" s="4">
-        <v>13978</v>
+        <v>1178</v>
       </c>
       <c r="Y20" s="4">
-        <v>796</v>
+        <v>2352</v>
       </c>
       <c r="Z20" s="4">
-        <v>8680</v>
+        <v>13416</v>
       </c>
       <c r="AA20" s="4">
-        <v>5756</v>
+        <v>14019</v>
       </c>
       <c r="AB20" s="4">
-        <v>11331</v>
+        <v>6738</v>
       </c>
       <c r="AC20" s="4">
-        <v>3276</v>
+        <v>3417</v>
       </c>
       <c r="AD20" s="4">
-        <v>13708</v>
+        <v>8415</v>
       </c>
       <c r="AE20" s="4">
-        <v>1425</v>
+        <v>14471</v>
       </c>
       <c r="AF20" s="4">
-        <v>12262</v>
+        <v>4711</v>
       </c>
       <c r="AG20" s="4">
-        <v>8014</v>
+        <v>6349</v>
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
-        <v>100020</v>
+        <v>100036</v>
       </c>
       <c r="B21" s="4">
-        <v>100020</v>
+        <v>100036</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="D21" s="4">
-        <v>8406</v>
+        <v>7325</v>
       </c>
       <c r="E21" s="4">
-        <v>12455</v>
+        <v>2317</v>
       </c>
       <c r="F21" s="4">
-        <v>270</v>
+        <v>5423</v>
       </c>
       <c r="G21" s="4">
-        <v>1825</v>
+        <v>9640</v>
       </c>
       <c r="H21" s="4">
-        <v>6881</v>
+        <v>13014</v>
       </c>
       <c r="I21" s="4">
-        <v>10037</v>
+        <v>10307</v>
       </c>
       <c r="J21" s="4">
-        <v>5209</v>
+        <v>5806</v>
       </c>
       <c r="K21" s="4">
-        <v>4874</v>
+        <v>9703</v>
       </c>
       <c r="L21" s="4">
-        <v>5248</v>
+        <v>9913</v>
       </c>
       <c r="M21" s="4">
-        <v>100020</v>
+        <v>100036</v>
       </c>
       <c r="N21" s="4">
-        <v>1790</v>
+        <v>2996</v>
       </c>
       <c r="O21" s="4">
-        <v>11224</v>
+        <v>2098</v>
       </c>
       <c r="P21" s="4">
-        <v>14092</v>
+        <v>9203</v>
       </c>
       <c r="Q21" s="4">
-        <v>12553</v>
+        <v>2902</v>
       </c>
       <c r="R21" s="4">
-        <v>708</v>
+        <v>9421</v>
       </c>
       <c r="S21" s="4">
-        <v>14010</v>
+        <v>13359</v>
       </c>
       <c r="T21" s="4">
-        <v>1899</v>
+        <v>2411</v>
       </c>
       <c r="U21" s="4">
-        <v>8138</v>
+        <v>5425</v>
       </c>
       <c r="V21" s="4">
-        <v>9218</v>
+        <v>13579</v>
       </c>
       <c r="W21" s="4">
-        <v>1821</v>
+        <v>12450</v>
       </c>
       <c r="X21" s="4">
-        <v>13093</v>
+        <v>8553</v>
       </c>
       <c r="Y21" s="4">
-        <v>13921</v>
+        <v>2477</v>
       </c>
       <c r="Z21" s="4">
-        <v>14591</v>
+        <v>6239</v>
       </c>
       <c r="AA21" s="4">
-        <v>8612</v>
+        <v>8349</v>
       </c>
       <c r="AB21" s="4">
-        <v>10357</v>
+        <v>4329</v>
       </c>
       <c r="AC21" s="4">
-        <v>9654</v>
+        <v>11087</v>
       </c>
       <c r="AD21" s="4">
-        <v>11867</v>
+        <v>13971</v>
       </c>
       <c r="AE21" s="4">
-        <v>5515</v>
+        <v>3447</v>
       </c>
       <c r="AF21" s="4">
-        <v>11184</v>
+        <v>14830</v>
       </c>
       <c r="AG21" s="4">
-        <v>10997</v>
+        <v>7157</v>
       </c>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <v>100021</v>
+        <v>100001</v>
       </c>
       <c r="B22" s="4">
-        <v>100021</v>
+        <v>100004</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D22" s="4">
-        <v>1634</v>
+        <v>7373</v>
       </c>
       <c r="E22" s="4">
-        <v>11101</v>
+        <v>10390</v>
       </c>
       <c r="F22" s="4">
-        <v>1136</v>
+        <v>2576</v>
       </c>
       <c r="G22" s="4">
-        <v>3397</v>
+        <v>7111</v>
       </c>
       <c r="H22" s="4">
-        <v>11309</v>
+        <v>14539</v>
       </c>
       <c r="I22" s="4">
-        <v>9316</v>
+        <v>5438</v>
       </c>
       <c r="J22" s="4">
-        <v>10344</v>
+        <v>13982</v>
       </c>
       <c r="K22" s="4">
-        <v>8100</v>
+        <v>11222</v>
       </c>
       <c r="L22" s="4">
-        <v>8172</v>
+        <v>13463</v>
       </c>
       <c r="M22" s="4">
-        <v>100021</v>
+        <v>100004</v>
       </c>
       <c r="N22" s="4">
-        <v>363</v>
+        <v>0</v>
       </c>
       <c r="O22" s="4">
-        <v>14168</v>
+        <v>12886</v>
       </c>
       <c r="P22" s="4">
-        <v>2985</v>
+        <v>957</v>
       </c>
       <c r="Q22" s="4">
-        <v>10875</v>
+        <v>13603</v>
       </c>
       <c r="R22" s="4">
-        <v>3066</v>
+        <v>13677</v>
       </c>
       <c r="S22" s="4">
-        <v>11857</v>
+        <v>10328</v>
       </c>
       <c r="T22" s="4">
-        <v>1418</v>
+        <v>1020</v>
       </c>
       <c r="U22" s="4">
-        <v>6395</v>
+        <v>4911</v>
       </c>
       <c r="V22" s="4">
-        <v>3316</v>
+        <v>3148</v>
       </c>
       <c r="W22" s="4">
-        <v>4530</v>
+        <v>4666</v>
       </c>
       <c r="X22" s="4">
-        <v>7723</v>
+        <v>1848</v>
       </c>
       <c r="Y22" s="4">
-        <v>7100</v>
+        <v>6053</v>
       </c>
       <c r="Z22" s="4">
-        <v>14983</v>
+        <v>11509</v>
       </c>
       <c r="AA22" s="4">
-        <v>4519</v>
+        <v>10482</v>
       </c>
       <c r="AB22" s="4">
-        <v>582</v>
+        <v>12388</v>
       </c>
       <c r="AC22" s="4">
-        <v>7752</v>
+        <v>8930</v>
       </c>
       <c r="AD22" s="4">
-        <v>13958</v>
+        <v>255</v>
       </c>
       <c r="AE22" s="4">
-        <v>9016</v>
+        <v>10857</v>
       </c>
       <c r="AF22" s="4">
-        <v>12055</v>
+        <v>13375</v>
       </c>
       <c r="AG22" s="4">
-        <v>9312</v>
+        <v>9654</v>
       </c>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
-        <v>100022</v>
+        <v>100042</v>
       </c>
       <c r="B23" s="4">
-        <v>100022</v>
+        <v>100042</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="D23" s="4">
-        <v>249</v>
+        <v>7516</v>
       </c>
       <c r="E23" s="4">
-        <v>3427</v>
+        <v>1743</v>
       </c>
       <c r="F23" s="4">
-        <v>8301</v>
+        <v>6074</v>
       </c>
       <c r="G23" s="4">
-        <v>5203</v>
+        <v>5849</v>
       </c>
       <c r="H23" s="4">
-        <v>8225</v>
+        <v>3980</v>
       </c>
       <c r="I23" s="4">
-        <v>5726</v>
+        <v>12018</v>
       </c>
       <c r="J23" s="4">
-        <v>13191</v>
+        <v>8420</v>
       </c>
       <c r="K23" s="4">
-        <v>10102</v>
+        <v>5361</v>
       </c>
       <c r="L23" s="4">
-        <v>2057</v>
+        <v>579</v>
       </c>
       <c r="M23" s="4">
-        <v>100022</v>
+        <v>100042</v>
       </c>
       <c r="N23" s="4">
-        <v>2206</v>
+        <v>1659</v>
       </c>
       <c r="O23" s="4">
-        <v>4083</v>
+        <v>14200</v>
       </c>
       <c r="P23" s="4">
-        <v>12180</v>
+        <v>10378</v>
       </c>
       <c r="Q23" s="4">
-        <v>5849</v>
+        <v>14210</v>
       </c>
       <c r="R23" s="4">
-        <v>3749</v>
+        <v>4222</v>
       </c>
       <c r="S23" s="4">
-        <v>838</v>
+        <v>4344</v>
       </c>
       <c r="T23" s="4">
         <v>0</v>
       </c>
       <c r="U23" s="4">
-        <v>8841</v>
+        <v>3412</v>
       </c>
       <c r="V23" s="4">
-        <v>6702</v>
+        <v>7518</v>
       </c>
       <c r="W23" s="4">
-        <v>9791</v>
+        <v>8266</v>
       </c>
       <c r="X23" s="4">
-        <v>3592</v>
+        <v>4393</v>
       </c>
       <c r="Y23" s="4">
-        <v>11271</v>
+        <v>4956</v>
       </c>
       <c r="Z23" s="4">
-        <v>8729</v>
+        <v>14565</v>
       </c>
       <c r="AA23" s="4">
-        <v>8802</v>
+        <v>11809</v>
       </c>
       <c r="AB23" s="4">
-        <v>4423</v>
+        <v>10277</v>
       </c>
       <c r="AC23" s="4">
-        <v>14070</v>
+        <v>1183</v>
       </c>
       <c r="AD23" s="4">
-        <v>2885</v>
+        <v>4582</v>
       </c>
       <c r="AE23" s="4">
-        <v>874</v>
+        <v>3284</v>
       </c>
       <c r="AF23" s="4">
-        <v>7996</v>
+        <v>14953</v>
       </c>
       <c r="AG23" s="4">
-        <v>2334</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
@@ -3992,2325 +3992,2325 @@
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <v>100024</v>
+        <v>100025</v>
       </c>
       <c r="B25" s="4">
-        <v>100024</v>
+        <v>100025</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D25" s="4">
-        <v>10323</v>
+        <v>7785</v>
       </c>
       <c r="E25" s="4">
-        <v>14380</v>
+        <v>4022</v>
       </c>
       <c r="F25" s="4">
-        <v>1953</v>
+        <v>10456</v>
       </c>
       <c r="G25" s="4">
-        <v>12308</v>
+        <v>11279</v>
       </c>
       <c r="H25" s="4">
-        <v>9545</v>
+        <v>10974</v>
       </c>
       <c r="I25" s="4">
-        <v>3005</v>
+        <v>13246</v>
       </c>
       <c r="J25" s="4">
-        <v>10139</v>
+        <v>8149</v>
       </c>
       <c r="K25" s="4">
-        <v>8070</v>
+        <v>1686</v>
       </c>
       <c r="L25" s="4">
-        <v>7718</v>
+        <v>11363</v>
       </c>
       <c r="M25" s="4">
-        <v>100024</v>
+        <v>100025</v>
       </c>
       <c r="N25" s="4">
-        <v>748</v>
+        <v>1466</v>
       </c>
       <c r="O25" s="4">
-        <v>10946</v>
+        <v>9453</v>
       </c>
       <c r="P25" s="4">
-        <v>8185</v>
+        <v>10828</v>
       </c>
       <c r="Q25" s="4">
-        <v>10707</v>
+        <v>4566</v>
       </c>
       <c r="R25" s="4">
-        <v>1301</v>
+        <v>944</v>
       </c>
       <c r="S25" s="4">
-        <v>89</v>
+        <v>12207</v>
       </c>
       <c r="T25" s="4">
         <v>0</v>
       </c>
       <c r="U25" s="4">
-        <v>5159</v>
+        <v>9113</v>
       </c>
       <c r="V25" s="4">
-        <v>5957</v>
+        <v>12613</v>
       </c>
       <c r="W25" s="4">
-        <v>2263</v>
+        <v>11669</v>
       </c>
       <c r="X25" s="4">
-        <v>9974</v>
+        <v>12161</v>
       </c>
       <c r="Y25" s="4">
-        <v>14584</v>
+        <v>3720</v>
       </c>
       <c r="Z25" s="4">
-        <v>13281</v>
+        <v>10581</v>
       </c>
       <c r="AA25" s="4">
-        <v>11479</v>
+        <v>7738</v>
       </c>
       <c r="AB25" s="4">
-        <v>6730</v>
+        <v>2066</v>
       </c>
       <c r="AC25" s="4">
-        <v>14377</v>
+        <v>11747</v>
       </c>
       <c r="AD25" s="4">
-        <v>11797</v>
+        <v>12098</v>
       </c>
       <c r="AE25" s="4">
-        <v>14322</v>
+        <v>6886</v>
       </c>
       <c r="AF25" s="4">
-        <v>3406</v>
+        <v>11283</v>
       </c>
       <c r="AG25" s="4">
-        <v>5260</v>
+        <v>6972</v>
       </c>
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
-        <v>100025</v>
+        <v>100029</v>
       </c>
       <c r="B26" s="4">
-        <v>100025</v>
+        <v>100029</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D26" s="4">
-        <v>7785</v>
+        <v>8072</v>
       </c>
       <c r="E26" s="4">
-        <v>4022</v>
+        <v>13968</v>
       </c>
       <c r="F26" s="4">
-        <v>10456</v>
+        <v>13959</v>
       </c>
       <c r="G26" s="4">
-        <v>11279</v>
+        <v>7050</v>
       </c>
       <c r="H26" s="4">
-        <v>10974</v>
+        <v>1817</v>
       </c>
       <c r="I26" s="4">
-        <v>13246</v>
+        <v>5729</v>
       </c>
       <c r="J26" s="4">
-        <v>8149</v>
+        <v>9442</v>
       </c>
       <c r="K26" s="4">
-        <v>1686</v>
+        <v>13119</v>
       </c>
       <c r="L26" s="4">
-        <v>11363</v>
+        <v>12991</v>
       </c>
       <c r="M26" s="4">
-        <v>100025</v>
+        <v>100029</v>
       </c>
       <c r="N26" s="4">
-        <v>1466</v>
+        <v>2149</v>
       </c>
       <c r="O26" s="4">
-        <v>9453</v>
+        <v>8241</v>
       </c>
       <c r="P26" s="4">
-        <v>10828</v>
+        <v>3135</v>
       </c>
       <c r="Q26" s="4">
-        <v>4566</v>
+        <v>6025</v>
       </c>
       <c r="R26" s="4">
-        <v>944</v>
+        <v>9540</v>
       </c>
       <c r="S26" s="4">
-        <v>12207</v>
+        <v>2505</v>
       </c>
       <c r="T26" s="4">
-        <v>0</v>
+        <v>1784</v>
       </c>
       <c r="U26" s="4">
-        <v>9113</v>
+        <v>13470</v>
       </c>
       <c r="V26" s="4">
-        <v>12613</v>
+        <v>9082</v>
       </c>
       <c r="W26" s="4">
-        <v>11669</v>
+        <v>3576</v>
       </c>
       <c r="X26" s="4">
-        <v>12161</v>
+        <v>3077</v>
       </c>
       <c r="Y26" s="4">
-        <v>3720</v>
+        <v>7142</v>
       </c>
       <c r="Z26" s="4">
-        <v>10581</v>
+        <v>2516</v>
       </c>
       <c r="AA26" s="4">
-        <v>7738</v>
+        <v>13467</v>
       </c>
       <c r="AB26" s="4">
-        <v>2066</v>
+        <v>7964</v>
       </c>
       <c r="AC26" s="4">
-        <v>11747</v>
+        <v>6365</v>
       </c>
       <c r="AD26" s="4">
-        <v>12098</v>
+        <v>13059</v>
       </c>
       <c r="AE26" s="4">
-        <v>6886</v>
+        <v>14387</v>
       </c>
       <c r="AF26" s="4">
-        <v>11283</v>
+        <v>4935</v>
       </c>
       <c r="AG26" s="4">
-        <v>6972</v>
+        <v>9417</v>
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
-        <v>100026</v>
+        <v>100009</v>
       </c>
       <c r="B27" s="4">
-        <v>100026</v>
+        <v>100013</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="D27" s="4">
-        <v>6893</v>
+        <v>8083</v>
       </c>
       <c r="E27" s="4">
-        <v>13593</v>
+        <v>7056</v>
       </c>
       <c r="F27" s="4">
-        <v>1513</v>
+        <v>2488</v>
       </c>
       <c r="G27" s="4">
-        <v>6964</v>
+        <v>11520</v>
       </c>
       <c r="H27" s="4">
-        <v>9619</v>
+        <v>2005</v>
       </c>
       <c r="I27" s="4">
-        <v>9209</v>
+        <v>13584</v>
       </c>
       <c r="J27" s="4">
-        <v>1013</v>
+        <v>7027</v>
       </c>
       <c r="K27" s="4">
-        <v>9209</v>
+        <v>8729</v>
       </c>
       <c r="L27" s="4">
-        <v>6878</v>
+        <v>818</v>
       </c>
       <c r="M27" s="4">
-        <v>100026</v>
+        <v>100013</v>
       </c>
       <c r="N27" s="4">
-        <v>2095</v>
+        <v>1707</v>
       </c>
       <c r="O27" s="4">
-        <v>12215</v>
+        <v>1449</v>
       </c>
       <c r="P27" s="4">
-        <v>7158</v>
+        <v>8057</v>
       </c>
       <c r="Q27" s="4">
-        <v>1043</v>
+        <v>2195</v>
       </c>
       <c r="R27" s="4">
-        <v>13310</v>
+        <v>2567</v>
       </c>
       <c r="S27" s="4">
-        <v>9280</v>
+        <v>1741</v>
       </c>
       <c r="T27" s="4">
         <v>0</v>
       </c>
       <c r="U27" s="4">
-        <v>2443</v>
+        <v>9576</v>
       </c>
       <c r="V27" s="4">
-        <v>1726</v>
+        <v>6433</v>
       </c>
       <c r="W27" s="4">
-        <v>156</v>
+        <v>14299</v>
       </c>
       <c r="X27" s="4">
-        <v>4003</v>
+        <v>7892</v>
       </c>
       <c r="Y27" s="4">
-        <v>9756</v>
+        <v>11301</v>
       </c>
       <c r="Z27" s="4">
-        <v>10504</v>
+        <v>9695</v>
       </c>
       <c r="AA27" s="4">
-        <v>1429</v>
+        <v>1391</v>
       </c>
       <c r="AB27" s="4">
-        <v>10357</v>
+        <v>14533</v>
       </c>
       <c r="AC27" s="4">
-        <v>5782</v>
+        <v>8357</v>
       </c>
       <c r="AD27" s="4">
-        <v>8738</v>
+        <v>7357</v>
       </c>
       <c r="AE27" s="4">
-        <v>8037</v>
+        <v>12018</v>
       </c>
       <c r="AF27" s="4">
-        <v>5544</v>
+        <v>12535</v>
       </c>
       <c r="AG27" s="4">
-        <v>6311</v>
+        <v>9544</v>
       </c>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
-        <v>100027</v>
+        <v>100020</v>
       </c>
       <c r="B28" s="4">
-        <v>100027</v>
+        <v>100020</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D28" s="4">
-        <v>2787</v>
+        <v>8406</v>
       </c>
       <c r="E28" s="4">
-        <v>5002</v>
+        <v>12455</v>
       </c>
       <c r="F28" s="4">
-        <v>12062</v>
+        <v>270</v>
       </c>
       <c r="G28" s="4">
-        <v>14451</v>
+        <v>1825</v>
       </c>
       <c r="H28" s="4">
-        <v>11582</v>
+        <v>6881</v>
       </c>
       <c r="I28" s="4">
-        <v>4303</v>
+        <v>10037</v>
       </c>
       <c r="J28" s="4">
-        <v>3177</v>
+        <v>5209</v>
       </c>
       <c r="K28" s="4">
-        <v>13993</v>
+        <v>4874</v>
       </c>
       <c r="L28" s="4">
-        <v>5552</v>
+        <v>5248</v>
       </c>
       <c r="M28" s="4">
-        <v>100027</v>
+        <v>100020</v>
       </c>
       <c r="N28" s="4">
-        <v>380</v>
+        <v>1790</v>
       </c>
       <c r="O28" s="4">
-        <v>6028</v>
+        <v>11224</v>
       </c>
       <c r="P28" s="4">
-        <v>14493</v>
+        <v>14092</v>
       </c>
       <c r="Q28" s="4">
-        <v>1392</v>
+        <v>12553</v>
       </c>
       <c r="R28" s="4">
-        <v>2314</v>
+        <v>708</v>
       </c>
       <c r="S28" s="4">
-        <v>9267</v>
+        <v>14010</v>
       </c>
       <c r="T28" s="4">
-        <v>0</v>
+        <v>1899</v>
       </c>
       <c r="U28" s="4">
-        <v>2950</v>
+        <v>8138</v>
       </c>
       <c r="V28" s="4">
-        <v>4642</v>
+        <v>9218</v>
       </c>
       <c r="W28" s="4">
-        <v>973</v>
+        <v>1821</v>
       </c>
       <c r="X28" s="4">
-        <v>5032</v>
+        <v>13093</v>
       </c>
       <c r="Y28" s="4">
-        <v>874</v>
+        <v>13921</v>
       </c>
       <c r="Z28" s="4">
-        <v>3732</v>
+        <v>14591</v>
       </c>
       <c r="AA28" s="4">
-        <v>7188</v>
+        <v>8612</v>
       </c>
       <c r="AB28" s="4">
-        <v>2099</v>
+        <v>10357</v>
       </c>
       <c r="AC28" s="4">
-        <v>6125</v>
+        <v>9654</v>
       </c>
       <c r="AD28" s="4">
-        <v>6403</v>
+        <v>11867</v>
       </c>
       <c r="AE28" s="4">
-        <v>1441</v>
+        <v>5515</v>
       </c>
       <c r="AF28" s="4">
-        <v>10064</v>
+        <v>11184</v>
       </c>
       <c r="AG28" s="4">
-        <v>1217</v>
+        <v>10997</v>
       </c>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
-        <v>100028</v>
+        <v>100001</v>
       </c>
       <c r="B29" s="4">
-        <v>100028</v>
+        <v>100008</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="D29" s="4">
-        <v>6754</v>
+        <v>8879</v>
       </c>
       <c r="E29" s="4">
-        <v>9902</v>
+        <v>5665</v>
       </c>
       <c r="F29" s="4">
-        <v>2593</v>
+        <v>1413</v>
       </c>
       <c r="G29" s="4">
-        <v>10405</v>
+        <v>14308</v>
       </c>
       <c r="H29" s="4">
-        <v>12297</v>
+        <v>9197</v>
       </c>
       <c r="I29" s="4">
-        <v>320</v>
+        <v>12968</v>
       </c>
       <c r="J29" s="4">
-        <v>2205</v>
+        <v>11079</v>
       </c>
       <c r="K29" s="4">
-        <v>12552</v>
+        <v>3878</v>
       </c>
       <c r="L29" s="4">
-        <v>2065</v>
+        <v>9527</v>
       </c>
       <c r="M29" s="4">
-        <v>100028</v>
+        <v>100008</v>
       </c>
       <c r="N29" s="4">
-        <v>2241</v>
+        <v>1638</v>
       </c>
       <c r="O29" s="4">
-        <v>7632</v>
+        <v>9580</v>
       </c>
       <c r="P29" s="4">
-        <v>6220</v>
+        <v>4286</v>
       </c>
       <c r="Q29" s="4">
-        <v>10388</v>
+        <v>14628</v>
       </c>
       <c r="R29" s="4">
-        <v>4185</v>
+        <v>12712</v>
       </c>
       <c r="S29" s="4">
-        <v>6907</v>
+        <v>6422</v>
       </c>
       <c r="T29" s="4">
-        <v>1608</v>
+        <v>2323</v>
       </c>
       <c r="U29" s="4">
-        <v>169</v>
+        <v>9492</v>
       </c>
       <c r="V29" s="4">
-        <v>9190</v>
+        <v>7664</v>
       </c>
       <c r="W29" s="4">
-        <v>5120</v>
+        <v>2934</v>
       </c>
       <c r="X29" s="4">
-        <v>6593</v>
+        <v>5692</v>
       </c>
       <c r="Y29" s="4">
-        <v>3519</v>
+        <v>14526</v>
       </c>
       <c r="Z29" s="4">
-        <v>2790</v>
+        <v>4612</v>
       </c>
       <c r="AA29" s="4">
-        <v>3417</v>
+        <v>2757</v>
       </c>
       <c r="AB29" s="4">
-        <v>7370</v>
+        <v>5989</v>
       </c>
       <c r="AC29" s="4">
-        <v>12028</v>
+        <v>8718</v>
       </c>
       <c r="AD29" s="4">
-        <v>3728</v>
+        <v>10611</v>
       </c>
       <c r="AE29" s="4">
-        <v>3714</v>
+        <v>7261</v>
       </c>
       <c r="AF29" s="4">
-        <v>3555</v>
+        <v>1931</v>
       </c>
       <c r="AG29" s="4">
-        <v>3275</v>
+        <v>12570</v>
       </c>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
-        <v>100029</v>
+        <v>100009</v>
       </c>
       <c r="B30" s="4">
-        <v>100029</v>
+        <v>100010</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="D30" s="4">
-        <v>8072</v>
+        <v>9223</v>
       </c>
       <c r="E30" s="4">
-        <v>13968</v>
+        <v>9733</v>
       </c>
       <c r="F30" s="4">
-        <v>13959</v>
+        <v>1553</v>
       </c>
       <c r="G30" s="4">
-        <v>7050</v>
+        <v>9891</v>
       </c>
       <c r="H30" s="4">
-        <v>1817</v>
+        <v>13978</v>
       </c>
       <c r="I30" s="4">
-        <v>5729</v>
+        <v>2736</v>
       </c>
       <c r="J30" s="4">
-        <v>9442</v>
+        <v>901</v>
       </c>
       <c r="K30" s="4">
-        <v>13119</v>
+        <v>4237</v>
       </c>
       <c r="L30" s="4">
-        <v>12991</v>
+        <v>11291</v>
       </c>
       <c r="M30" s="4">
-        <v>100029</v>
+        <v>100010</v>
       </c>
       <c r="N30" s="4">
-        <v>2149</v>
+        <v>1943</v>
       </c>
       <c r="O30" s="4">
-        <v>8241</v>
+        <v>8545</v>
       </c>
       <c r="P30" s="4">
-        <v>3135</v>
+        <v>5809</v>
       </c>
       <c r="Q30" s="4">
-        <v>6025</v>
+        <v>9538</v>
       </c>
       <c r="R30" s="4">
-        <v>9540</v>
+        <v>6887</v>
       </c>
       <c r="S30" s="4">
-        <v>2505</v>
+        <v>13211</v>
       </c>
       <c r="T30" s="4">
-        <v>1784</v>
+        <v>1095</v>
       </c>
       <c r="U30" s="4">
-        <v>13470</v>
+        <v>7513</v>
       </c>
       <c r="V30" s="4">
-        <v>9082</v>
+        <v>1903</v>
       </c>
       <c r="W30" s="4">
-        <v>3576</v>
+        <v>8028</v>
       </c>
       <c r="X30" s="4">
-        <v>3077</v>
+        <v>4792</v>
       </c>
       <c r="Y30" s="4">
-        <v>7142</v>
+        <v>2798</v>
       </c>
       <c r="Z30" s="4">
-        <v>2516</v>
+        <v>9759</v>
       </c>
       <c r="AA30" s="4">
-        <v>13467</v>
+        <v>9644</v>
       </c>
       <c r="AB30" s="4">
-        <v>7964</v>
+        <v>793</v>
       </c>
       <c r="AC30" s="4">
-        <v>6365</v>
+        <v>10522</v>
       </c>
       <c r="AD30" s="4">
-        <v>13059</v>
+        <v>6990</v>
       </c>
       <c r="AE30" s="4">
-        <v>14387</v>
+        <v>9297</v>
       </c>
       <c r="AF30" s="4">
-        <v>4935</v>
+        <v>7812</v>
       </c>
       <c r="AG30" s="4">
-        <v>9417</v>
+        <v>5121</v>
       </c>
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
-        <v>100030</v>
+        <v>100024</v>
       </c>
       <c r="B31" s="4">
-        <v>100030</v>
+        <v>100024</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D31" s="4">
-        <v>3622</v>
+        <v>10323</v>
       </c>
       <c r="E31" s="4">
-        <v>1851</v>
+        <v>14380</v>
       </c>
       <c r="F31" s="4">
-        <v>696</v>
+        <v>1953</v>
       </c>
       <c r="G31" s="4">
-        <v>2588</v>
+        <v>12308</v>
       </c>
       <c r="H31" s="4">
-        <v>2257</v>
+        <v>9545</v>
       </c>
       <c r="I31" s="4">
-        <v>6448</v>
+        <v>3005</v>
       </c>
       <c r="J31" s="4">
-        <v>8034</v>
+        <v>10139</v>
       </c>
       <c r="K31" s="4">
-        <v>4823</v>
+        <v>8070</v>
       </c>
       <c r="L31" s="4">
-        <v>1196</v>
+        <v>7718</v>
       </c>
       <c r="M31" s="4">
-        <v>100030</v>
+        <v>100024</v>
       </c>
       <c r="N31" s="4">
+        <v>748</v>
+      </c>
+      <c r="O31" s="4">
+        <v>10946</v>
+      </c>
+      <c r="P31" s="4">
+        <v>8185</v>
+      </c>
+      <c r="Q31" s="4">
+        <v>10707</v>
+      </c>
+      <c r="R31" s="4">
+        <v>1301</v>
+      </c>
+      <c r="S31" s="4">
+        <v>89</v>
+      </c>
+      <c r="T31" s="4">
         <v>0</v>
       </c>
-      <c r="O31" s="4">
-        <v>9864</v>
-      </c>
-      <c r="P31" s="4">
-        <v>8602</v>
-      </c>
-      <c r="Q31" s="4">
-        <v>2313</v>
-      </c>
-      <c r="R31" s="4">
-        <v>13099</v>
-      </c>
-      <c r="S31" s="4">
-        <v>12109</v>
-      </c>
-      <c r="T31" s="4">
-        <v>311</v>
-      </c>
       <c r="U31" s="4">
-        <v>4885</v>
+        <v>5159</v>
       </c>
       <c r="V31" s="4">
-        <v>3251</v>
+        <v>5957</v>
       </c>
       <c r="W31" s="4">
-        <v>5022</v>
+        <v>2263</v>
       </c>
       <c r="X31" s="4">
-        <v>11661</v>
+        <v>9974</v>
       </c>
       <c r="Y31" s="4">
-        <v>4968</v>
+        <v>14584</v>
       </c>
       <c r="Z31" s="4">
-        <v>8583</v>
+        <v>13281</v>
       </c>
       <c r="AA31" s="4">
-        <v>276</v>
+        <v>11479</v>
       </c>
       <c r="AB31" s="4">
-        <v>4813</v>
+        <v>6730</v>
       </c>
       <c r="AC31" s="4">
-        <v>8408</v>
+        <v>14377</v>
       </c>
       <c r="AD31" s="4">
-        <v>11700</v>
+        <v>11797</v>
       </c>
       <c r="AE31" s="4">
-        <v>11193</v>
+        <v>14322</v>
       </c>
       <c r="AF31" s="4">
-        <v>4826</v>
+        <v>3406</v>
       </c>
       <c r="AG31" s="4">
-        <v>10215</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
-        <v>100031</v>
+        <v>100038</v>
       </c>
       <c r="B32" s="4">
-        <v>100031</v>
+        <v>100038</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D32" s="4">
-        <v>1194</v>
+        <v>10501</v>
       </c>
       <c r="E32" s="4">
-        <v>9864</v>
+        <v>12601</v>
       </c>
       <c r="F32" s="4">
-        <v>12614</v>
+        <v>1605</v>
       </c>
       <c r="G32" s="4">
-        <v>241</v>
+        <v>856</v>
       </c>
       <c r="H32" s="4">
-        <v>14626</v>
+        <v>9415</v>
       </c>
       <c r="I32" s="4">
-        <v>427</v>
+        <v>11496</v>
       </c>
       <c r="J32" s="4">
-        <v>9967</v>
+        <v>7491</v>
       </c>
       <c r="K32" s="4">
-        <v>12454</v>
+        <v>9974</v>
       </c>
       <c r="L32" s="4">
-        <v>10408</v>
+        <v>2378</v>
       </c>
       <c r="M32" s="4">
-        <v>100031</v>
+        <v>100038</v>
       </c>
       <c r="N32" s="4">
-        <v>1121</v>
+        <v>1202</v>
       </c>
       <c r="O32" s="4">
-        <v>8170</v>
+        <v>14076</v>
       </c>
       <c r="P32" s="4">
-        <v>5070</v>
+        <v>3450</v>
       </c>
       <c r="Q32" s="4">
-        <v>10421</v>
+        <v>13454</v>
       </c>
       <c r="R32" s="4">
-        <v>409</v>
+        <v>12985</v>
       </c>
       <c r="S32" s="4">
-        <v>10573</v>
+        <v>4072</v>
       </c>
       <c r="T32" s="4">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="U32" s="4">
-        <v>7635</v>
+        <v>5520</v>
       </c>
       <c r="V32" s="4">
-        <v>6322</v>
+        <v>14147</v>
       </c>
       <c r="W32" s="4">
-        <v>14300</v>
+        <v>3183</v>
       </c>
       <c r="X32" s="4">
-        <v>3022</v>
+        <v>12163</v>
       </c>
       <c r="Y32" s="4">
-        <v>14013</v>
+        <v>13967</v>
       </c>
       <c r="Z32" s="4">
-        <v>515</v>
+        <v>8664</v>
       </c>
       <c r="AA32" s="4">
-        <v>5033</v>
+        <v>3876</v>
       </c>
       <c r="AB32" s="4">
-        <v>2292</v>
+        <v>6853</v>
       </c>
       <c r="AC32" s="4">
-        <v>7824</v>
+        <v>8637</v>
       </c>
       <c r="AD32" s="4">
-        <v>13252</v>
+        <v>11300</v>
       </c>
       <c r="AE32" s="4">
-        <v>7365</v>
+        <v>14271</v>
       </c>
       <c r="AF32" s="4">
-        <v>11596</v>
+        <v>9389</v>
       </c>
       <c r="AG32" s="4">
-        <v>7422</v>
+        <v>3695</v>
       </c>
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
-        <v>100032</v>
+        <v>100001</v>
       </c>
       <c r="B33" s="4">
-        <v>100032</v>
+        <v>100002</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="D33" s="4">
-        <v>13686</v>
+        <v>11398</v>
       </c>
       <c r="E33" s="4">
-        <v>8827</v>
+        <v>927</v>
       </c>
       <c r="F33" s="4">
-        <v>4454</v>
+        <v>8118</v>
       </c>
       <c r="G33" s="4">
-        <v>8629</v>
+        <v>5822</v>
       </c>
       <c r="H33" s="4">
-        <v>13202</v>
+        <v>14680</v>
       </c>
       <c r="I33" s="4">
-        <v>10990</v>
+        <v>12429</v>
       </c>
       <c r="J33" s="4">
-        <v>3604</v>
+        <v>10233</v>
       </c>
       <c r="K33" s="4">
-        <v>3286</v>
+        <v>14264</v>
       </c>
       <c r="L33" s="4">
-        <v>10392</v>
+        <v>1602</v>
       </c>
       <c r="M33" s="4">
-        <v>100032</v>
+        <v>100002</v>
       </c>
       <c r="N33" s="4">
-        <v>2947</v>
+        <v>0</v>
       </c>
       <c r="O33" s="4">
-        <v>470</v>
+        <v>6372</v>
       </c>
       <c r="P33" s="4">
-        <v>13518</v>
+        <v>1229</v>
       </c>
       <c r="Q33" s="4">
-        <v>10758</v>
+        <v>6753</v>
       </c>
       <c r="R33" s="4">
-        <v>3964</v>
+        <v>12658</v>
       </c>
       <c r="S33" s="4">
-        <v>13305</v>
+        <v>6362</v>
       </c>
       <c r="T33" s="4">
-        <v>0</v>
+        <v>2066</v>
       </c>
       <c r="U33" s="4">
-        <v>3315</v>
+        <v>1286</v>
       </c>
       <c r="V33" s="4">
-        <v>12285</v>
+        <v>3231</v>
       </c>
       <c r="W33" s="4">
-        <v>8045</v>
+        <v>82</v>
       </c>
       <c r="X33" s="4">
-        <v>7184</v>
+        <v>4382</v>
       </c>
       <c r="Y33" s="4">
-        <v>221</v>
+        <v>10439</v>
       </c>
       <c r="Z33" s="4">
-        <v>2649</v>
+        <v>5200</v>
       </c>
       <c r="AA33" s="4">
-        <v>7009</v>
+        <v>1230</v>
       </c>
       <c r="AB33" s="4">
-        <v>5082</v>
+        <v>12004</v>
       </c>
       <c r="AC33" s="4">
-        <v>13494</v>
+        <v>11826</v>
       </c>
       <c r="AD33" s="4">
-        <v>6194</v>
+        <v>4405</v>
       </c>
       <c r="AE33" s="4">
-        <v>296</v>
+        <v>10788</v>
       </c>
       <c r="AF33" s="4">
-        <v>11531</v>
+        <v>13555</v>
       </c>
       <c r="AG33" s="4">
-        <v>8969</v>
+        <v>327</v>
       </c>
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
-        <v>100033</v>
+        <v>100001</v>
       </c>
       <c r="B34" s="4">
-        <v>100033</v>
+        <v>100005</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="D34" s="4">
-        <v>3236</v>
+        <v>11445</v>
       </c>
       <c r="E34" s="4">
-        <v>2087</v>
+        <v>1103</v>
       </c>
       <c r="F34" s="4">
-        <v>2682</v>
+        <v>4522</v>
       </c>
       <c r="G34" s="4">
-        <v>2332</v>
+        <v>10791</v>
       </c>
       <c r="H34" s="4">
-        <v>4096</v>
+        <v>12233</v>
       </c>
       <c r="I34" s="4">
-        <v>14322</v>
+        <v>3495</v>
       </c>
       <c r="J34" s="4">
-        <v>10485</v>
+        <v>11423</v>
       </c>
       <c r="K34" s="4">
-        <v>14146</v>
+        <v>3604</v>
       </c>
       <c r="L34" s="4">
-        <v>7369</v>
+        <v>14908</v>
       </c>
       <c r="M34" s="4">
-        <v>100033</v>
+        <v>100005</v>
       </c>
       <c r="N34" s="4">
-        <v>1804</v>
+        <v>1006</v>
       </c>
       <c r="O34" s="4">
-        <v>8153</v>
+        <v>10369</v>
       </c>
       <c r="P34" s="4">
-        <v>6283</v>
+        <v>11579</v>
       </c>
       <c r="Q34" s="4">
-        <v>3246</v>
+        <v>13239</v>
       </c>
       <c r="R34" s="4">
-        <v>12036</v>
+        <v>10010</v>
       </c>
       <c r="S34" s="4">
-        <v>12812</v>
+        <v>14924</v>
       </c>
       <c r="T34" s="4">
-        <v>289</v>
+        <v>1307</v>
       </c>
       <c r="U34" s="4">
-        <v>9151</v>
+        <v>14667</v>
       </c>
       <c r="V34" s="4">
-        <v>13443</v>
+        <v>5464</v>
       </c>
       <c r="W34" s="4">
-        <v>66</v>
+        <v>1238</v>
       </c>
       <c r="X34" s="4">
-        <v>14894</v>
+        <v>3765</v>
       </c>
       <c r="Y34" s="4">
-        <v>14554</v>
+        <v>872</v>
       </c>
       <c r="Z34" s="4">
-        <v>8268</v>
+        <v>11045</v>
       </c>
       <c r="AA34" s="4">
-        <v>8833</v>
+        <v>789</v>
       </c>
       <c r="AB34" s="4">
-        <v>11153</v>
+        <v>7228</v>
       </c>
       <c r="AC34" s="4">
-        <v>2047</v>
+        <v>9577</v>
       </c>
       <c r="AD34" s="4">
-        <v>311</v>
+        <v>11776</v>
       </c>
       <c r="AE34" s="4">
-        <v>9319</v>
+        <v>5756</v>
       </c>
       <c r="AF34" s="4">
-        <v>11424</v>
+        <v>9044</v>
       </c>
       <c r="AG34" s="4">
-        <v>12653</v>
+        <v>303</v>
       </c>
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
-        <v>100034</v>
+        <v>100009</v>
       </c>
       <c r="B35" s="4">
-        <v>100034</v>
+        <v>100012</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="D35" s="4">
-        <v>398</v>
+        <v>11626</v>
       </c>
       <c r="E35" s="4">
-        <v>4409</v>
+        <v>12878</v>
       </c>
       <c r="F35" s="4">
-        <v>10894</v>
+        <v>4677</v>
       </c>
       <c r="G35" s="4">
-        <v>10830</v>
+        <v>13037</v>
       </c>
       <c r="H35" s="4">
-        <v>10146</v>
+        <v>6520</v>
       </c>
       <c r="I35" s="4">
-        <v>12711</v>
+        <v>8098</v>
       </c>
       <c r="J35" s="4">
-        <v>2445</v>
+        <v>9238</v>
       </c>
       <c r="K35" s="4">
-        <v>3611</v>
+        <v>11764</v>
       </c>
       <c r="L35" s="4">
-        <v>5354</v>
+        <v>10264</v>
       </c>
       <c r="M35" s="4">
-        <v>100034</v>
+        <v>100012</v>
       </c>
       <c r="N35" s="4">
-        <v>572</v>
+        <v>1648</v>
       </c>
       <c r="O35" s="4">
-        <v>5720</v>
+        <v>3960</v>
       </c>
       <c r="P35" s="4">
-        <v>3219</v>
+        <v>10579</v>
       </c>
       <c r="Q35" s="4">
-        <v>14167</v>
+        <v>11117</v>
       </c>
       <c r="R35" s="4">
-        <v>8444</v>
+        <v>10327</v>
       </c>
       <c r="S35" s="4">
-        <v>8585</v>
+        <v>1017</v>
       </c>
       <c r="T35" s="4">
-        <v>503</v>
+        <v>1585</v>
       </c>
       <c r="U35" s="4">
-        <v>14427</v>
+        <v>5765</v>
       </c>
       <c r="V35" s="4">
-        <v>3252</v>
+        <v>4188</v>
       </c>
       <c r="W35" s="4">
-        <v>5425</v>
+        <v>12825</v>
       </c>
       <c r="X35" s="4">
-        <v>4896</v>
+        <v>5708</v>
       </c>
       <c r="Y35" s="4">
-        <v>2977</v>
+        <v>8889</v>
       </c>
       <c r="Z35" s="4">
-        <v>3219</v>
+        <v>12725</v>
       </c>
       <c r="AA35" s="4">
-        <v>7824</v>
+        <v>10692</v>
       </c>
       <c r="AB35" s="4">
-        <v>13226</v>
+        <v>1431</v>
       </c>
       <c r="AC35" s="4">
-        <v>5562</v>
+        <v>10269</v>
       </c>
       <c r="AD35" s="4">
-        <v>8195</v>
+        <v>6722</v>
       </c>
       <c r="AE35" s="4">
-        <v>5419</v>
+        <v>10202</v>
       </c>
       <c r="AF35" s="4">
-        <v>10811</v>
+        <v>1262</v>
       </c>
       <c r="AG35" s="4">
-        <v>10875</v>
+        <v>6870</v>
       </c>
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
-        <v>100035</v>
+        <v>100015</v>
       </c>
       <c r="B36" s="4">
-        <v>100035</v>
+        <v>100015</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="D36" s="4">
-        <v>7007</v>
+        <v>11902</v>
       </c>
       <c r="E36" s="4">
-        <v>2233</v>
+        <v>13178</v>
       </c>
       <c r="F36" s="4">
-        <v>14847</v>
+        <v>10395</v>
       </c>
       <c r="G36" s="4">
-        <v>5152</v>
+        <v>10529</v>
       </c>
       <c r="H36" s="4">
-        <v>14812</v>
+        <v>298</v>
       </c>
       <c r="I36" s="4">
-        <v>13869</v>
+        <v>12341</v>
       </c>
       <c r="J36" s="4">
-        <v>13614</v>
+        <v>9666</v>
       </c>
       <c r="K36" s="4">
-        <v>14857</v>
+        <v>5693</v>
       </c>
       <c r="L36" s="4">
-        <v>11253</v>
+        <v>8412</v>
       </c>
       <c r="M36" s="4">
-        <v>100035</v>
+        <v>100015</v>
       </c>
       <c r="N36" s="4">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="O36" s="4">
-        <v>1267</v>
+        <v>5214</v>
       </c>
       <c r="P36" s="4">
-        <v>9192</v>
+        <v>12755</v>
       </c>
       <c r="Q36" s="4">
-        <v>7194</v>
+        <v>14930</v>
       </c>
       <c r="R36" s="4">
-        <v>8365</v>
+        <v>13548</v>
       </c>
       <c r="S36" s="4">
-        <v>8479</v>
+        <v>1782</v>
       </c>
       <c r="T36" s="4">
-        <v>830</v>
+        <v>2364</v>
       </c>
       <c r="U36" s="4">
-        <v>1573</v>
+        <v>6173</v>
       </c>
       <c r="V36" s="4">
-        <v>4583</v>
+        <v>13094</v>
       </c>
       <c r="W36" s="4">
-        <v>3192</v>
+        <v>2764</v>
       </c>
       <c r="X36" s="4">
-        <v>2473</v>
+        <v>8750</v>
       </c>
       <c r="Y36" s="4">
-        <v>7351</v>
+        <v>647</v>
       </c>
       <c r="Z36" s="4">
-        <v>6487</v>
+        <v>3004</v>
       </c>
       <c r="AA36" s="4">
-        <v>7923</v>
+        <v>2756</v>
       </c>
       <c r="AB36" s="4">
-        <v>9951</v>
+        <v>14278</v>
       </c>
       <c r="AC36" s="4">
-        <v>1419</v>
+        <v>7556</v>
       </c>
       <c r="AD36" s="4">
-        <v>6468</v>
+        <v>4733</v>
       </c>
       <c r="AE36" s="4">
-        <v>272</v>
+        <v>10396</v>
       </c>
       <c r="AF36" s="4">
-        <v>13785</v>
+        <v>8497</v>
       </c>
       <c r="AG36" s="4">
-        <v>11345</v>
+        <v>8184</v>
       </c>
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
-        <v>100036</v>
+        <v>100019</v>
       </c>
       <c r="B37" s="4">
-        <v>100036</v>
+        <v>100019</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="D37" s="4">
-        <v>7325</v>
+        <v>12128</v>
       </c>
       <c r="E37" s="4">
-        <v>2317</v>
+        <v>9235</v>
       </c>
       <c r="F37" s="4">
-        <v>5423</v>
+        <v>14270</v>
       </c>
       <c r="G37" s="4">
-        <v>9640</v>
+        <v>598</v>
       </c>
       <c r="H37" s="4">
-        <v>13014</v>
+        <v>1125</v>
       </c>
       <c r="I37" s="4">
-        <v>10307</v>
+        <v>11412</v>
       </c>
       <c r="J37" s="4">
-        <v>5806</v>
+        <v>13656</v>
       </c>
       <c r="K37" s="4">
-        <v>9703</v>
+        <v>3219</v>
       </c>
       <c r="L37" s="4">
-        <v>9913</v>
+        <v>5261</v>
       </c>
       <c r="M37" s="4">
-        <v>100036</v>
+        <v>100019</v>
       </c>
       <c r="N37" s="4">
-        <v>2996</v>
+        <v>1303</v>
       </c>
       <c r="O37" s="4">
-        <v>2098</v>
+        <v>503</v>
       </c>
       <c r="P37" s="4">
-        <v>9203</v>
+        <v>2646</v>
       </c>
       <c r="Q37" s="4">
-        <v>2902</v>
+        <v>13569</v>
       </c>
       <c r="R37" s="4">
-        <v>9421</v>
+        <v>3367</v>
       </c>
       <c r="S37" s="4">
-        <v>13359</v>
+        <v>4422</v>
       </c>
       <c r="T37" s="4">
-        <v>2411</v>
+        <v>1652</v>
       </c>
       <c r="U37" s="4">
-        <v>5425</v>
+        <v>7664</v>
       </c>
       <c r="V37" s="4">
-        <v>13579</v>
+        <v>2715</v>
       </c>
       <c r="W37" s="4">
-        <v>12450</v>
+        <v>5909</v>
       </c>
       <c r="X37" s="4">
-        <v>8553</v>
+        <v>13978</v>
       </c>
       <c r="Y37" s="4">
-        <v>2477</v>
+        <v>796</v>
       </c>
       <c r="Z37" s="4">
-        <v>6239</v>
+        <v>8680</v>
       </c>
       <c r="AA37" s="4">
-        <v>8349</v>
+        <v>5756</v>
       </c>
       <c r="AB37" s="4">
-        <v>4329</v>
+        <v>11331</v>
       </c>
       <c r="AC37" s="4">
-        <v>11087</v>
+        <v>3276</v>
       </c>
       <c r="AD37" s="4">
-        <v>13971</v>
+        <v>13708</v>
       </c>
       <c r="AE37" s="4">
-        <v>3447</v>
+        <v>1425</v>
       </c>
       <c r="AF37" s="4">
-        <v>14830</v>
+        <v>12262</v>
       </c>
       <c r="AG37" s="4">
-        <v>7157</v>
+        <v>8014</v>
       </c>
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
-        <v>100037</v>
+        <v>100016</v>
       </c>
       <c r="B38" s="4">
-        <v>100037</v>
+        <v>100016</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="D38" s="4">
-        <v>14617</v>
+        <v>12254</v>
       </c>
       <c r="E38" s="4">
-        <v>1345</v>
+        <v>2057</v>
       </c>
       <c r="F38" s="4">
-        <v>12658</v>
+        <v>14802</v>
       </c>
       <c r="G38" s="4">
-        <v>11142</v>
+        <v>9822</v>
       </c>
       <c r="H38" s="4">
-        <v>8584</v>
+        <v>5180</v>
       </c>
       <c r="I38" s="4">
-        <v>10675</v>
+        <v>11919</v>
       </c>
       <c r="J38" s="4">
-        <v>9582</v>
+        <v>12656</v>
       </c>
       <c r="K38" s="4">
-        <v>10270</v>
+        <v>3024</v>
       </c>
       <c r="L38" s="4">
-        <v>4315</v>
+        <v>9998</v>
       </c>
       <c r="M38" s="4">
-        <v>100037</v>
+        <v>100016</v>
       </c>
       <c r="N38" s="4">
-        <v>1779</v>
+        <v>2571</v>
       </c>
       <c r="O38" s="4">
-        <v>2360</v>
+        <v>13475</v>
       </c>
       <c r="P38" s="4">
-        <v>6573</v>
+        <v>11319</v>
       </c>
       <c r="Q38" s="4">
-        <v>8496</v>
+        <v>2661</v>
       </c>
       <c r="R38" s="4">
-        <v>7392</v>
+        <v>9746</v>
       </c>
       <c r="S38" s="4">
-        <v>8915</v>
+        <v>11971</v>
       </c>
       <c r="T38" s="4">
-        <v>978</v>
+        <v>1647</v>
       </c>
       <c r="U38" s="4">
-        <v>14780</v>
+        <v>9054</v>
       </c>
       <c r="V38" s="4">
-        <v>11702</v>
+        <v>14340</v>
       </c>
       <c r="W38" s="4">
-        <v>13576</v>
+        <v>12452</v>
       </c>
       <c r="X38" s="4">
-        <v>477</v>
+        <v>340</v>
       </c>
       <c r="Y38" s="4">
-        <v>9429</v>
+        <v>11471</v>
       </c>
       <c r="Z38" s="4">
-        <v>14613</v>
+        <v>2771</v>
       </c>
       <c r="AA38" s="4">
-        <v>8282</v>
+        <v>8911</v>
       </c>
       <c r="AB38" s="4">
-        <v>6884</v>
+        <v>7057</v>
       </c>
       <c r="AC38" s="4">
-        <v>9554</v>
+        <v>12853</v>
       </c>
       <c r="AD38" s="4">
-        <v>5849</v>
+        <v>10684</v>
       </c>
       <c r="AE38" s="4">
-        <v>4532</v>
+        <v>8724</v>
       </c>
       <c r="AF38" s="4">
-        <v>5064</v>
+        <v>3139</v>
       </c>
       <c r="AG38" s="4">
-        <v>8493</v>
+        <v>12150</v>
       </c>
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
-        <v>100038</v>
+        <v>100041</v>
       </c>
       <c r="B39" s="4">
-        <v>100038</v>
+        <v>100041</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D39" s="4">
-        <v>10501</v>
+        <v>12437</v>
       </c>
       <c r="E39" s="4">
-        <v>12601</v>
+        <v>9599</v>
       </c>
       <c r="F39" s="4">
-        <v>1605</v>
+        <v>6944</v>
       </c>
       <c r="G39" s="4">
-        <v>856</v>
+        <v>6769</v>
       </c>
       <c r="H39" s="4">
-        <v>9415</v>
+        <v>3573</v>
       </c>
       <c r="I39" s="4">
-        <v>11496</v>
+        <v>11753</v>
       </c>
       <c r="J39" s="4">
-        <v>7491</v>
+        <v>12502</v>
       </c>
       <c r="K39" s="4">
-        <v>9974</v>
+        <v>11939</v>
       </c>
       <c r="L39" s="4">
-        <v>2378</v>
+        <v>10222</v>
       </c>
       <c r="M39" s="4">
-        <v>100038</v>
+        <v>100041</v>
       </c>
       <c r="N39" s="4">
-        <v>1202</v>
+        <v>355</v>
       </c>
       <c r="O39" s="4">
-        <v>14076</v>
+        <v>10291</v>
       </c>
       <c r="P39" s="4">
-        <v>3450</v>
+        <v>14014</v>
       </c>
       <c r="Q39" s="4">
-        <v>13454</v>
+        <v>9378</v>
       </c>
       <c r="R39" s="4">
-        <v>12985</v>
+        <v>8610</v>
       </c>
       <c r="S39" s="4">
-        <v>4072</v>
+        <v>3473</v>
       </c>
       <c r="T39" s="4">
         <v>0</v>
       </c>
       <c r="U39" s="4">
-        <v>5520</v>
+        <v>3987</v>
       </c>
       <c r="V39" s="4">
-        <v>14147</v>
+        <v>4898</v>
       </c>
       <c r="W39" s="4">
-        <v>3183</v>
+        <v>9645</v>
       </c>
       <c r="X39" s="4">
-        <v>12163</v>
+        <v>10216</v>
       </c>
       <c r="Y39" s="4">
-        <v>13967</v>
+        <v>12890</v>
       </c>
       <c r="Z39" s="4">
-        <v>8664</v>
+        <v>5438</v>
       </c>
       <c r="AA39" s="4">
-        <v>3876</v>
+        <v>14853</v>
       </c>
       <c r="AB39" s="4">
-        <v>6853</v>
+        <v>1597</v>
       </c>
       <c r="AC39" s="4">
-        <v>8637</v>
+        <v>4197</v>
       </c>
       <c r="AD39" s="4">
-        <v>11300</v>
+        <v>11599</v>
       </c>
       <c r="AE39" s="4">
-        <v>14271</v>
+        <v>4421</v>
       </c>
       <c r="AF39" s="4">
-        <v>9389</v>
+        <v>6385</v>
       </c>
       <c r="AG39" s="4">
-        <v>3695</v>
+        <v>7054</v>
       </c>
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
-        <v>100039</v>
+        <v>100044</v>
       </c>
       <c r="B40" s="4">
-        <v>100039</v>
+        <v>100044</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D40" s="4">
-        <v>14080</v>
+        <v>12453</v>
       </c>
       <c r="E40" s="4">
-        <v>11819</v>
+        <v>11144</v>
       </c>
       <c r="F40" s="4">
-        <v>9217</v>
+        <v>14707</v>
       </c>
       <c r="G40" s="4">
-        <v>7496</v>
+        <v>10598</v>
       </c>
       <c r="H40" s="4">
-        <v>14517</v>
+        <v>1671</v>
       </c>
       <c r="I40" s="4">
-        <v>9699</v>
+        <v>306</v>
       </c>
       <c r="J40" s="4">
-        <v>3514</v>
+        <v>7486</v>
       </c>
       <c r="K40" s="4">
-        <v>6397</v>
+        <v>14423</v>
       </c>
       <c r="L40" s="4">
-        <v>1848</v>
+        <v>2319</v>
       </c>
       <c r="M40" s="4">
-        <v>100039</v>
+        <v>100044</v>
       </c>
       <c r="N40" s="4">
-        <v>2883</v>
+        <v>2472</v>
       </c>
       <c r="O40" s="4">
-        <v>11190</v>
+        <v>9959</v>
       </c>
       <c r="P40" s="4">
-        <v>11038</v>
+        <v>7337</v>
       </c>
       <c r="Q40" s="4">
-        <v>7403</v>
+        <v>2429</v>
       </c>
       <c r="R40" s="4">
-        <v>10895</v>
+        <v>4962</v>
       </c>
       <c r="S40" s="4">
-        <v>13443</v>
+        <v>13993</v>
       </c>
       <c r="T40" s="4">
-        <v>469</v>
+        <v>0</v>
       </c>
       <c r="U40" s="4">
-        <v>7221</v>
+        <v>2430</v>
       </c>
       <c r="V40" s="4">
-        <v>6782</v>
+        <v>10477</v>
       </c>
       <c r="W40" s="4">
-        <v>1347</v>
+        <v>6210</v>
       </c>
       <c r="X40" s="4">
-        <v>12244</v>
+        <v>10737</v>
       </c>
       <c r="Y40" s="4">
-        <v>3301</v>
+        <v>9722</v>
       </c>
       <c r="Z40" s="4">
-        <v>14584</v>
+        <v>11877</v>
       </c>
       <c r="AA40" s="4">
-        <v>13937</v>
+        <v>13118</v>
       </c>
       <c r="AB40" s="4">
-        <v>1577</v>
+        <v>12806</v>
       </c>
       <c r="AC40" s="4">
-        <v>10441</v>
+        <v>1803</v>
       </c>
       <c r="AD40" s="4">
-        <v>10078</v>
+        <v>3899</v>
       </c>
       <c r="AE40" s="4">
-        <v>11084</v>
+        <v>11503</v>
       </c>
       <c r="AF40" s="4">
-        <v>14666</v>
+        <v>12574</v>
       </c>
       <c r="AG40" s="4">
-        <v>14476</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
-        <v>100040</v>
+        <v>100018</v>
       </c>
       <c r="B41" s="4">
-        <v>100040</v>
+        <v>100018</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="D41" s="4">
-        <v>7094</v>
+        <v>13165</v>
       </c>
       <c r="E41" s="4">
-        <v>373</v>
+        <v>2492</v>
       </c>
       <c r="F41" s="4">
-        <v>660</v>
+        <v>2719</v>
       </c>
       <c r="G41" s="4">
-        <v>9045</v>
+        <v>2441</v>
       </c>
       <c r="H41" s="4">
-        <v>10029</v>
+        <v>3348</v>
       </c>
       <c r="I41" s="4">
-        <v>13304</v>
+        <v>8110</v>
       </c>
       <c r="J41" s="4">
-        <v>6575</v>
+        <v>13581</v>
       </c>
       <c r="K41" s="4">
-        <v>7051</v>
+        <v>1930</v>
       </c>
       <c r="L41" s="4">
-        <v>13100</v>
+        <v>11697</v>
       </c>
       <c r="M41" s="4">
-        <v>100040</v>
+        <v>100018</v>
       </c>
       <c r="N41" s="4">
-        <v>1996</v>
+        <v>2000</v>
       </c>
       <c r="O41" s="4">
-        <v>3686</v>
+        <v>6205</v>
       </c>
       <c r="P41" s="4">
+        <v>14826</v>
+      </c>
+      <c r="Q41" s="4">
+        <v>7925</v>
+      </c>
+      <c r="R41" s="4">
+        <v>1212</v>
+      </c>
+      <c r="S41" s="4">
+        <v>11307</v>
+      </c>
+      <c r="T41" s="4">
+        <v>0</v>
+      </c>
+      <c r="U41" s="4">
+        <v>9424</v>
+      </c>
+      <c r="V41" s="4">
+        <v>7037</v>
+      </c>
+      <c r="W41" s="4">
+        <v>11378</v>
+      </c>
+      <c r="X41" s="4">
         <v>4703</v>
       </c>
-      <c r="Q41" s="4">
-        <v>5200</v>
-      </c>
-      <c r="R41" s="4">
-        <v>3218</v>
-      </c>
-      <c r="S41" s="4">
-        <v>11205</v>
-      </c>
-      <c r="T41" s="4">
-        <v>746</v>
-      </c>
-      <c r="U41" s="4">
-        <v>14981</v>
-      </c>
-      <c r="V41" s="4">
-        <v>10403</v>
-      </c>
-      <c r="W41" s="4">
-        <v>3287</v>
-      </c>
-      <c r="X41" s="4">
-        <v>1178</v>
-      </c>
       <c r="Y41" s="4">
-        <v>2352</v>
+        <v>14141</v>
       </c>
       <c r="Z41" s="4">
-        <v>13416</v>
+        <v>2415</v>
       </c>
       <c r="AA41" s="4">
-        <v>14019</v>
+        <v>9146</v>
       </c>
       <c r="AB41" s="4">
-        <v>6738</v>
+        <v>14739</v>
       </c>
       <c r="AC41" s="4">
-        <v>3417</v>
+        <v>1716</v>
       </c>
       <c r="AD41" s="4">
-        <v>8415</v>
+        <v>945</v>
       </c>
       <c r="AE41" s="4">
-        <v>14471</v>
+        <v>10244</v>
       </c>
       <c r="AF41" s="4">
-        <v>4711</v>
+        <v>6285</v>
       </c>
       <c r="AG41" s="4">
-        <v>6349</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
-        <v>100041</v>
+        <v>100017</v>
       </c>
       <c r="B42" s="4">
-        <v>100041</v>
+        <v>100017</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="D42" s="4">
-        <v>12437</v>
+        <v>13336</v>
       </c>
       <c r="E42" s="4">
-        <v>9599</v>
+        <v>7707</v>
       </c>
       <c r="F42" s="4">
-        <v>6944</v>
+        <v>12329</v>
       </c>
       <c r="G42" s="4">
-        <v>6769</v>
+        <v>6981</v>
       </c>
       <c r="H42" s="4">
-        <v>3573</v>
+        <v>920</v>
       </c>
       <c r="I42" s="4">
-        <v>11753</v>
+        <v>10591</v>
       </c>
       <c r="J42" s="4">
-        <v>12502</v>
+        <v>7374</v>
       </c>
       <c r="K42" s="4">
-        <v>11939</v>
+        <v>7704</v>
       </c>
       <c r="L42" s="4">
-        <v>10222</v>
+        <v>4904</v>
       </c>
       <c r="M42" s="4">
-        <v>100041</v>
+        <v>100017</v>
       </c>
       <c r="N42" s="4">
-        <v>355</v>
+        <v>514</v>
       </c>
       <c r="O42" s="4">
-        <v>10291</v>
+        <v>13364</v>
       </c>
       <c r="P42" s="4">
-        <v>14014</v>
+        <v>14042</v>
       </c>
       <c r="Q42" s="4">
-        <v>9378</v>
+        <v>573</v>
       </c>
       <c r="R42" s="4">
-        <v>8610</v>
+        <v>5785</v>
       </c>
       <c r="S42" s="4">
-        <v>3473</v>
+        <v>3244</v>
       </c>
       <c r="T42" s="4">
-        <v>0</v>
+        <v>1531</v>
       </c>
       <c r="U42" s="4">
-        <v>3987</v>
+        <v>14921</v>
       </c>
       <c r="V42" s="4">
-        <v>4898</v>
+        <v>9354</v>
       </c>
       <c r="W42" s="4">
-        <v>9645</v>
+        <v>5163</v>
       </c>
       <c r="X42" s="4">
-        <v>10216</v>
+        <v>8289</v>
       </c>
       <c r="Y42" s="4">
-        <v>12890</v>
+        <v>11896</v>
       </c>
       <c r="Z42" s="4">
-        <v>5438</v>
+        <v>12191</v>
       </c>
       <c r="AA42" s="4">
-        <v>14853</v>
+        <v>7556</v>
       </c>
       <c r="AB42" s="4">
-        <v>1597</v>
+        <v>9454</v>
       </c>
       <c r="AC42" s="4">
-        <v>4197</v>
+        <v>1721</v>
       </c>
       <c r="AD42" s="4">
-        <v>11599</v>
+        <v>13795</v>
       </c>
       <c r="AE42" s="4">
-        <v>4421</v>
+        <v>14871</v>
       </c>
       <c r="AF42" s="4">
-        <v>6385</v>
+        <v>5970</v>
       </c>
       <c r="AG42" s="4">
-        <v>7054</v>
+        <v>14863</v>
       </c>
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
-        <v>100042</v>
+        <v>100001</v>
       </c>
       <c r="B43" s="4">
-        <v>100042</v>
+        <v>100006</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="D43" s="4">
-        <v>7516</v>
+        <v>13384</v>
       </c>
       <c r="E43" s="4">
-        <v>1743</v>
+        <v>1228</v>
       </c>
       <c r="F43" s="4">
-        <v>6074</v>
+        <v>1885</v>
       </c>
       <c r="G43" s="4">
-        <v>5849</v>
+        <v>5655</v>
       </c>
       <c r="H43" s="4">
-        <v>3980</v>
+        <v>13891</v>
       </c>
       <c r="I43" s="4">
-        <v>12018</v>
+        <v>3756</v>
       </c>
       <c r="J43" s="4">
-        <v>8420</v>
+        <v>5810</v>
       </c>
       <c r="K43" s="4">
-        <v>5361</v>
+        <v>8463</v>
       </c>
       <c r="L43" s="4">
-        <v>579</v>
+        <v>8447</v>
       </c>
       <c r="M43" s="4">
-        <v>100042</v>
+        <v>100006</v>
       </c>
       <c r="N43" s="4">
-        <v>1659</v>
+        <v>0</v>
       </c>
       <c r="O43" s="4">
+        <v>11907</v>
+      </c>
+      <c r="P43" s="4">
         <v>14200</v>
       </c>
-      <c r="P43" s="4">
-        <v>10378</v>
-      </c>
       <c r="Q43" s="4">
-        <v>14210</v>
+        <v>3350</v>
       </c>
       <c r="R43" s="4">
-        <v>4222</v>
+        <v>9666</v>
       </c>
       <c r="S43" s="4">
-        <v>4344</v>
+        <v>1730</v>
       </c>
       <c r="T43" s="4">
-        <v>0</v>
+        <v>1764</v>
       </c>
       <c r="U43" s="4">
-        <v>3412</v>
+        <v>2357</v>
       </c>
       <c r="V43" s="4">
-        <v>7518</v>
+        <v>10889</v>
       </c>
       <c r="W43" s="4">
-        <v>8266</v>
+        <v>5571</v>
       </c>
       <c r="X43" s="4">
-        <v>4393</v>
+        <v>8249</v>
       </c>
       <c r="Y43" s="4">
-        <v>4956</v>
+        <v>5282</v>
       </c>
       <c r="Z43" s="4">
-        <v>14565</v>
+        <v>13987</v>
       </c>
       <c r="AA43" s="4">
-        <v>11809</v>
+        <v>3339</v>
       </c>
       <c r="AB43" s="4">
-        <v>10277</v>
+        <v>13347</v>
       </c>
       <c r="AC43" s="4">
-        <v>1183</v>
+        <v>11421</v>
       </c>
       <c r="AD43" s="4">
-        <v>4582</v>
+        <v>10176</v>
       </c>
       <c r="AE43" s="4">
-        <v>3284</v>
+        <v>5965</v>
       </c>
       <c r="AF43" s="4">
-        <v>14953</v>
+        <v>2178</v>
       </c>
       <c r="AG43" s="4">
-        <v>1841</v>
+        <v>6857</v>
       </c>
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
-        <v>100043</v>
+        <v>100001</v>
       </c>
       <c r="B44" s="4">
-        <v>100043</v>
+        <v>100003</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="D44" s="4">
-        <v>1039</v>
+        <v>13588</v>
       </c>
       <c r="E44" s="4">
-        <v>4309</v>
+        <v>3311</v>
       </c>
       <c r="F44" s="4">
-        <v>5415</v>
+        <v>9698</v>
       </c>
       <c r="G44" s="4">
-        <v>8939</v>
+        <v>13581</v>
       </c>
       <c r="H44" s="4">
-        <v>10404</v>
+        <v>433</v>
       </c>
       <c r="I44" s="4">
-        <v>11350</v>
+        <v>755</v>
       </c>
       <c r="J44" s="4">
-        <v>14400</v>
+        <v>3741</v>
       </c>
       <c r="K44" s="4">
-        <v>14232</v>
+        <v>13685</v>
       </c>
       <c r="L44" s="4">
-        <v>6263</v>
+        <v>10181</v>
       </c>
       <c r="M44" s="4">
-        <v>100043</v>
+        <v>100003</v>
       </c>
       <c r="N44" s="4">
-        <v>2488</v>
+        <v>0</v>
       </c>
       <c r="O44" s="4">
-        <v>7771</v>
+        <v>4117</v>
       </c>
       <c r="P44" s="4">
-        <v>13783</v>
+        <v>13539</v>
       </c>
       <c r="Q44" s="4">
-        <v>724</v>
+        <v>13901</v>
       </c>
       <c r="R44" s="4">
-        <v>13128</v>
+        <v>2050</v>
       </c>
       <c r="S44" s="4">
-        <v>3053</v>
+        <v>2061</v>
       </c>
       <c r="T44" s="4">
-        <v>0</v>
+        <v>1371</v>
       </c>
       <c r="U44" s="4">
-        <v>6159</v>
+        <v>12539</v>
       </c>
       <c r="V44" s="4">
-        <v>10574</v>
+        <v>9134</v>
       </c>
       <c r="W44" s="4">
-        <v>1557</v>
+        <v>9294</v>
       </c>
       <c r="X44" s="4">
-        <v>9476</v>
+        <v>455</v>
       </c>
       <c r="Y44" s="4">
-        <v>4902</v>
+        <v>3945</v>
       </c>
       <c r="Z44" s="4">
-        <v>5177</v>
+        <v>8402</v>
       </c>
       <c r="AA44" s="4">
-        <v>7145</v>
+        <v>14724</v>
       </c>
       <c r="AB44" s="4">
-        <v>7200</v>
+        <v>11481</v>
       </c>
       <c r="AC44" s="4">
-        <v>9575</v>
+        <v>4181</v>
       </c>
       <c r="AD44" s="4">
-        <v>5784</v>
+        <v>4229</v>
       </c>
       <c r="AE44" s="4">
-        <v>12903</v>
+        <v>2092</v>
       </c>
       <c r="AF44" s="4">
-        <v>157</v>
+        <v>8372</v>
       </c>
       <c r="AG44" s="4">
-        <v>9207</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
-        <v>100044</v>
+        <v>100032</v>
       </c>
       <c r="B45" s="4">
-        <v>100044</v>
+        <v>100032</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="D45" s="4">
-        <v>12453</v>
+        <v>13686</v>
       </c>
       <c r="E45" s="4">
-        <v>11144</v>
+        <v>8827</v>
       </c>
       <c r="F45" s="4">
-        <v>14707</v>
+        <v>4454</v>
       </c>
       <c r="G45" s="4">
-        <v>10598</v>
+        <v>8629</v>
       </c>
       <c r="H45" s="4">
-        <v>1671</v>
+        <v>13202</v>
       </c>
       <c r="I45" s="4">
-        <v>306</v>
+        <v>10990</v>
       </c>
       <c r="J45" s="4">
-        <v>7486</v>
+        <v>3604</v>
       </c>
       <c r="K45" s="4">
-        <v>14423</v>
+        <v>3286</v>
       </c>
       <c r="L45" s="4">
-        <v>2319</v>
+        <v>10392</v>
       </c>
       <c r="M45" s="4">
-        <v>100044</v>
+        <v>100032</v>
       </c>
       <c r="N45" s="4">
-        <v>2472</v>
+        <v>2947</v>
       </c>
       <c r="O45" s="4">
-        <v>9959</v>
+        <v>470</v>
       </c>
       <c r="P45" s="4">
-        <v>7337</v>
+        <v>13518</v>
       </c>
       <c r="Q45" s="4">
-        <v>2429</v>
+        <v>10758</v>
       </c>
       <c r="R45" s="4">
-        <v>4962</v>
+        <v>3964</v>
       </c>
       <c r="S45" s="4">
-        <v>13993</v>
+        <v>13305</v>
       </c>
       <c r="T45" s="4">
         <v>0</v>
       </c>
       <c r="U45" s="4">
-        <v>2430</v>
+        <v>3315</v>
       </c>
       <c r="V45" s="4">
-        <v>10477</v>
+        <v>12285</v>
       </c>
       <c r="W45" s="4">
-        <v>6210</v>
+        <v>8045</v>
       </c>
       <c r="X45" s="4">
-        <v>10737</v>
+        <v>7184</v>
       </c>
       <c r="Y45" s="4">
-        <v>9722</v>
+        <v>221</v>
       </c>
       <c r="Z45" s="4">
-        <v>11877</v>
+        <v>2649</v>
       </c>
       <c r="AA45" s="4">
-        <v>13118</v>
+        <v>7009</v>
       </c>
       <c r="AB45" s="4">
-        <v>12806</v>
+        <v>5082</v>
       </c>
       <c r="AC45" s="4">
-        <v>1803</v>
+        <v>13494</v>
       </c>
       <c r="AD45" s="4">
-        <v>3899</v>
+        <v>6194</v>
       </c>
       <c r="AE45" s="4">
-        <v>11503</v>
+        <v>296</v>
       </c>
       <c r="AF45" s="4">
-        <v>12574</v>
+        <v>11531</v>
       </c>
       <c r="AG45" s="4">
-        <v>1075</v>
+        <v>8969</v>
       </c>
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
-        <v>100045</v>
+        <v>100039</v>
       </c>
       <c r="B46" s="4">
-        <v>100045</v>
+        <v>100039</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D46" s="4">
-        <v>14701</v>
+        <v>14080</v>
       </c>
       <c r="E46" s="4">
-        <v>14783</v>
+        <v>11819</v>
       </c>
       <c r="F46" s="4">
-        <v>12441</v>
+        <v>9217</v>
       </c>
       <c r="G46" s="4">
-        <v>12637</v>
+        <v>7496</v>
       </c>
       <c r="H46" s="4">
-        <v>10520</v>
+        <v>14517</v>
       </c>
       <c r="I46" s="4">
-        <v>7075</v>
+        <v>9699</v>
       </c>
       <c r="J46" s="4">
-        <v>12375</v>
+        <v>3514</v>
       </c>
       <c r="K46" s="4">
-        <v>2951</v>
+        <v>6397</v>
       </c>
       <c r="L46" s="4">
-        <v>5345</v>
+        <v>1848</v>
       </c>
       <c r="M46" s="4">
-        <v>100045</v>
+        <v>100039</v>
       </c>
       <c r="N46" s="4">
-        <v>2508</v>
+        <v>2883</v>
       </c>
       <c r="O46" s="4">
-        <v>3401</v>
+        <v>11190</v>
       </c>
       <c r="P46" s="4">
-        <v>8348</v>
+        <v>11038</v>
       </c>
       <c r="Q46" s="4">
-        <v>11135</v>
+        <v>7403</v>
       </c>
       <c r="R46" s="4">
-        <v>9481</v>
+        <v>10895</v>
       </c>
       <c r="S46" s="4">
-        <v>9256</v>
+        <v>13443</v>
       </c>
       <c r="T46" s="4">
-        <v>0</v>
+        <v>469</v>
       </c>
       <c r="U46" s="4">
-        <v>1235</v>
+        <v>7221</v>
       </c>
       <c r="V46" s="4">
-        <v>9207</v>
+        <v>6782</v>
       </c>
       <c r="W46" s="4">
-        <v>6520</v>
+        <v>1347</v>
       </c>
       <c r="X46" s="4">
-        <v>10955</v>
+        <v>12244</v>
       </c>
       <c r="Y46" s="4">
-        <v>14682</v>
+        <v>3301</v>
       </c>
       <c r="Z46" s="4">
-        <v>4161</v>
+        <v>14584</v>
       </c>
       <c r="AA46" s="4">
-        <v>6985</v>
+        <v>13937</v>
       </c>
       <c r="AB46" s="4">
-        <v>12012</v>
+        <v>1577</v>
       </c>
       <c r="AC46" s="4">
-        <v>10810</v>
+        <v>10441</v>
       </c>
       <c r="AD46" s="4">
-        <v>13950</v>
+        <v>10078</v>
       </c>
       <c r="AE46" s="4">
-        <v>417</v>
+        <v>11084</v>
       </c>
       <c r="AF46" s="4">
-        <v>12630</v>
+        <v>14666</v>
       </c>
       <c r="AG46" s="4">
-        <v>3212</v>
+        <v>14476</v>
       </c>
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
-        <v>100046</v>
+        <v>100049</v>
       </c>
       <c r="B47" s="4">
-        <v>100046</v>
+        <v>100049</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D47" s="4">
-        <v>5421</v>
+        <v>14085</v>
       </c>
       <c r="E47" s="4">
-        <v>7841</v>
+        <v>13892</v>
       </c>
       <c r="F47" s="4">
-        <v>1073</v>
+        <v>9218</v>
       </c>
       <c r="G47" s="4">
-        <v>12205</v>
+        <v>5026</v>
       </c>
       <c r="H47" s="4">
-        <v>168</v>
+        <v>3087</v>
       </c>
       <c r="I47" s="4">
-        <v>5357</v>
+        <v>14418</v>
       </c>
       <c r="J47" s="4">
-        <v>3325</v>
+        <v>5567</v>
       </c>
       <c r="K47" s="4">
-        <v>4608</v>
+        <v>3282</v>
       </c>
       <c r="L47" s="4">
-        <v>6166</v>
+        <v>6525</v>
       </c>
       <c r="M47" s="4">
-        <v>100046</v>
+        <v>100049</v>
       </c>
       <c r="N47" s="4">
-        <v>0</v>
+        <v>2405</v>
       </c>
       <c r="O47" s="4">
-        <v>8502</v>
+        <v>3860</v>
       </c>
       <c r="P47" s="4">
-        <v>7982</v>
+        <v>13143</v>
       </c>
       <c r="Q47" s="4">
-        <v>9083</v>
+        <v>3098</v>
       </c>
       <c r="R47" s="4">
-        <v>13973</v>
+        <v>5142</v>
       </c>
       <c r="S47" s="4">
-        <v>1040</v>
+        <v>7806</v>
       </c>
       <c r="T47" s="4">
-        <v>2191</v>
+        <v>294</v>
       </c>
       <c r="U47" s="4">
-        <v>12976</v>
+        <v>14096</v>
       </c>
       <c r="V47" s="4">
-        <v>2563</v>
+        <v>609</v>
       </c>
       <c r="W47" s="4">
-        <v>4521</v>
+        <v>13135</v>
       </c>
       <c r="X47" s="4">
-        <v>624</v>
+        <v>7861</v>
       </c>
       <c r="Y47" s="4">
-        <v>12180</v>
+        <v>6347</v>
       </c>
       <c r="Z47" s="4">
-        <v>12757</v>
+        <v>11713</v>
       </c>
       <c r="AA47" s="4">
-        <v>3168</v>
+        <v>8960</v>
       </c>
       <c r="AB47" s="4">
-        <v>14461</v>
+        <v>14256</v>
       </c>
       <c r="AC47" s="4">
-        <v>12657</v>
+        <v>6702</v>
       </c>
       <c r="AD47" s="4">
-        <v>13652</v>
+        <v>1940</v>
       </c>
       <c r="AE47" s="4">
-        <v>13167</v>
+        <v>2355</v>
       </c>
       <c r="AF47" s="4">
-        <v>5624</v>
+        <v>603</v>
       </c>
       <c r="AG47" s="4">
-        <v>10248</v>
+        <v>9559</v>
       </c>
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
@@ -6416,308 +6416,313 @@
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
-        <v>100048</v>
+        <v>100037</v>
       </c>
       <c r="B49" s="4">
-        <v>100048</v>
+        <v>100037</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="D49" s="4">
-        <v>3497</v>
+        <v>14617</v>
       </c>
       <c r="E49" s="4">
-        <v>769</v>
+        <v>1345</v>
       </c>
       <c r="F49" s="4">
-        <v>3951</v>
+        <v>12658</v>
       </c>
       <c r="G49" s="4">
-        <v>5730</v>
+        <v>11142</v>
       </c>
       <c r="H49" s="4">
-        <v>7578</v>
+        <v>8584</v>
       </c>
       <c r="I49" s="4">
-        <v>13615</v>
+        <v>10675</v>
       </c>
       <c r="J49" s="4">
-        <v>8746</v>
+        <v>9582</v>
       </c>
       <c r="K49" s="4">
-        <v>9040</v>
+        <v>10270</v>
       </c>
       <c r="L49" s="4">
-        <v>12315</v>
+        <v>4315</v>
       </c>
       <c r="M49" s="4">
-        <v>100048</v>
+        <v>100037</v>
       </c>
       <c r="N49" s="4">
-        <v>2954</v>
+        <v>1779</v>
       </c>
       <c r="O49" s="4">
-        <v>7201</v>
+        <v>2360</v>
       </c>
       <c r="P49" s="4">
-        <v>12085</v>
+        <v>6573</v>
       </c>
       <c r="Q49" s="4">
-        <v>6377</v>
+        <v>8496</v>
       </c>
       <c r="R49" s="4">
-        <v>9557</v>
+        <v>7392</v>
       </c>
       <c r="S49" s="4">
-        <v>13154</v>
+        <v>8915</v>
       </c>
       <c r="T49" s="4">
-        <v>0</v>
+        <v>978</v>
       </c>
       <c r="U49" s="4">
-        <v>7097</v>
+        <v>14780</v>
       </c>
       <c r="V49" s="4">
-        <v>14508</v>
+        <v>11702</v>
       </c>
       <c r="W49" s="4">
-        <v>3142</v>
+        <v>13576</v>
       </c>
       <c r="X49" s="4">
-        <v>7133</v>
+        <v>477</v>
       </c>
       <c r="Y49" s="4">
-        <v>7742</v>
+        <v>9429</v>
       </c>
       <c r="Z49" s="4">
-        <v>5684</v>
+        <v>14613</v>
       </c>
       <c r="AA49" s="4">
-        <v>4322</v>
+        <v>8282</v>
       </c>
       <c r="AB49" s="4">
-        <v>1054</v>
+        <v>6884</v>
       </c>
       <c r="AC49" s="4">
-        <v>9564</v>
+        <v>9554</v>
       </c>
       <c r="AD49" s="4">
-        <v>11893</v>
+        <v>5849</v>
       </c>
       <c r="AE49" s="4">
-        <v>7529</v>
+        <v>4532</v>
       </c>
       <c r="AF49" s="4">
-        <v>5701</v>
+        <v>5064</v>
       </c>
       <c r="AG49" s="4">
-        <v>10859</v>
+        <v>8493</v>
       </c>
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
-        <v>100049</v>
+        <v>100045</v>
       </c>
       <c r="B50" s="4">
-        <v>100049</v>
+        <v>100045</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D50" s="4">
-        <v>14085</v>
+        <v>14701</v>
       </c>
       <c r="E50" s="4">
-        <v>13892</v>
+        <v>14783</v>
       </c>
       <c r="F50" s="4">
-        <v>9218</v>
+        <v>12441</v>
       </c>
       <c r="G50" s="4">
-        <v>5026</v>
+        <v>12637</v>
       </c>
       <c r="H50" s="4">
-        <v>3087</v>
+        <v>10520</v>
       </c>
       <c r="I50" s="4">
-        <v>14418</v>
+        <v>7075</v>
       </c>
       <c r="J50" s="4">
-        <v>5567</v>
+        <v>12375</v>
       </c>
       <c r="K50" s="4">
-        <v>3282</v>
+        <v>2951</v>
       </c>
       <c r="L50" s="4">
-        <v>6525</v>
+        <v>5345</v>
       </c>
       <c r="M50" s="4">
-        <v>100049</v>
+        <v>100045</v>
       </c>
       <c r="N50" s="4">
-        <v>2405</v>
+        <v>2508</v>
       </c>
       <c r="O50" s="4">
-        <v>3860</v>
+        <v>3401</v>
       </c>
       <c r="P50" s="4">
-        <v>13143</v>
+        <v>8348</v>
       </c>
       <c r="Q50" s="4">
-        <v>3098</v>
+        <v>11135</v>
       </c>
       <c r="R50" s="4">
-        <v>5142</v>
+        <v>9481</v>
       </c>
       <c r="S50" s="4">
-        <v>7806</v>
+        <v>9256</v>
       </c>
       <c r="T50" s="4">
-        <v>294</v>
+        <v>0</v>
       </c>
       <c r="U50" s="4">
-        <v>14096</v>
+        <v>1235</v>
       </c>
       <c r="V50" s="4">
-        <v>609</v>
+        <v>9207</v>
       </c>
       <c r="W50" s="4">
-        <v>13135</v>
+        <v>6520</v>
       </c>
       <c r="X50" s="4">
-        <v>7861</v>
+        <v>10955</v>
       </c>
       <c r="Y50" s="4">
-        <v>6347</v>
+        <v>14682</v>
       </c>
       <c r="Z50" s="4">
-        <v>11713</v>
+        <v>4161</v>
       </c>
       <c r="AA50" s="4">
-        <v>8960</v>
+        <v>6985</v>
       </c>
       <c r="AB50" s="4">
-        <v>14256</v>
+        <v>12012</v>
       </c>
       <c r="AC50" s="4">
-        <v>6702</v>
+        <v>10810</v>
       </c>
       <c r="AD50" s="4">
-        <v>1940</v>
+        <v>13950</v>
       </c>
       <c r="AE50" s="4">
-        <v>2355</v>
+        <v>417</v>
       </c>
       <c r="AF50" s="4">
-        <v>603</v>
+        <v>12630</v>
       </c>
       <c r="AG50" s="4">
-        <v>9559</v>
+        <v>3212</v>
       </c>
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
-        <v>100050</v>
+        <v>100009</v>
       </c>
       <c r="B51" s="4">
-        <v>100050</v>
+        <v>100014</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>155</v>
+        <v>119</v>
       </c>
       <c r="D51" s="4">
-        <v>3704</v>
+        <v>14878</v>
       </c>
       <c r="E51" s="4">
-        <v>4056</v>
+        <v>4362</v>
       </c>
       <c r="F51" s="4">
-        <v>14818</v>
+        <v>9794</v>
       </c>
       <c r="G51" s="4">
-        <v>1143</v>
+        <v>14480</v>
       </c>
       <c r="H51" s="4">
-        <v>6108</v>
+        <v>8152</v>
       </c>
       <c r="I51" s="4">
-        <v>14882</v>
+        <v>792</v>
       </c>
       <c r="J51" s="4">
-        <v>6866</v>
+        <v>8385</v>
       </c>
       <c r="K51" s="4">
-        <v>3352</v>
+        <v>12164</v>
       </c>
       <c r="L51" s="4">
-        <v>12533</v>
+        <v>14688</v>
       </c>
       <c r="M51" s="4">
-        <v>100050</v>
+        <v>100014</v>
       </c>
       <c r="N51" s="4">
-        <v>0</v>
+        <v>829</v>
       </c>
       <c r="O51" s="4">
-        <v>747</v>
+        <v>6537</v>
       </c>
       <c r="P51" s="4">
-        <v>6987</v>
+        <v>119</v>
       </c>
       <c r="Q51" s="4">
-        <v>8427</v>
+        <v>5406</v>
       </c>
       <c r="R51" s="4">
-        <v>9481</v>
+        <v>12292</v>
       </c>
       <c r="S51" s="4">
-        <v>1633</v>
+        <v>11974</v>
       </c>
       <c r="T51" s="4">
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="U51" s="4">
-        <v>6454</v>
+        <v>12756</v>
       </c>
       <c r="V51" s="4">
-        <v>5567</v>
+        <v>11320</v>
       </c>
       <c r="W51" s="4">
-        <v>10616</v>
+        <v>2860</v>
       </c>
       <c r="X51" s="4">
-        <v>14446</v>
+        <v>6135</v>
       </c>
       <c r="Y51" s="4">
-        <v>12113</v>
+        <v>6951</v>
       </c>
       <c r="Z51" s="4">
-        <v>1893</v>
+        <v>9707</v>
       </c>
       <c r="AA51" s="4">
-        <v>8700</v>
+        <v>14785</v>
       </c>
       <c r="AB51" s="4">
-        <v>6687</v>
+        <v>8055</v>
       </c>
       <c r="AC51" s="4">
-        <v>14803</v>
+        <v>13653</v>
       </c>
       <c r="AD51" s="4">
-        <v>1632</v>
+        <v>5687</v>
       </c>
       <c r="AE51" s="4">
-        <v>9791</v>
+        <v>6968</v>
       </c>
       <c r="AF51" s="4">
-        <v>2177</v>
+        <v>252</v>
       </c>
       <c r="AG51" s="4">
-        <v>6997</v>
+        <v>14194</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AG51" xr:uid="{D8B1E343-19A0-4368-9346-1A3EB3E99462}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AG51">
+      <sortCondition ref="D1:D51"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
